--- a/artfynd/A 48490-2022 artfynd.xlsx
+++ b/artfynd/A 48490-2022 artfynd.xlsx
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121354210</v>
+        <v>121354148</v>
       </c>
       <c r="B7" t="n">
-        <v>98049</v>
+        <v>101240</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>221235</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696874</v>
+        <v>696853</v>
       </c>
       <c r="R7" t="n">
-        <v>6660666</v>
+        <v>6660481</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121354148</v>
+        <v>121354210</v>
       </c>
       <c r="B8" t="n">
-        <v>101240</v>
+        <v>98049</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221235</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696853</v>
+        <v>696874</v>
       </c>
       <c r="R8" t="n">
-        <v>6660481</v>
+        <v>6660666</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 48490-2022 artfynd.xlsx
+++ b/artfynd/A 48490-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121354251</v>
+        <v>121354216</v>
       </c>
       <c r="B2" t="n">
-        <v>90121</v>
+        <v>91630</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4191</v>
+        <v>4769</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Geastrum michelianum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Berk. &amp; Broome</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>696840</v>
+        <v>696818</v>
       </c>
       <c r="R2" t="n">
-        <v>6660674</v>
+        <v>6660846</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121354152</v>
+        <v>121354206</v>
       </c>
       <c r="B3" t="n">
-        <v>91620</v>
+        <v>98059</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>696860</v>
+        <v>696910</v>
       </c>
       <c r="R3" t="n">
-        <v>6660584</v>
+        <v>6660863</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121354249</v>
+        <v>121354218</v>
       </c>
       <c r="B4" t="n">
-        <v>100246</v>
+        <v>100256</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>696815</v>
+        <v>696810</v>
       </c>
       <c r="R4" t="n">
-        <v>6660731</v>
+        <v>6660842</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121354254</v>
+        <v>121354202</v>
       </c>
       <c r="B5" t="n">
-        <v>100246</v>
+        <v>100256</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696815</v>
+        <v>696939</v>
       </c>
       <c r="R5" t="n">
-        <v>6660713</v>
+        <v>6660882</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121354241</v>
+        <v>121354247</v>
       </c>
       <c r="B6" t="n">
-        <v>100246</v>
+        <v>100256</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696825</v>
+        <v>696845</v>
       </c>
       <c r="R6" t="n">
-        <v>6660796</v>
+        <v>6660742</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121354148</v>
+        <v>121354254</v>
       </c>
       <c r="B7" t="n">
-        <v>101240</v>
+        <v>100256</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696853</v>
+        <v>696815</v>
       </c>
       <c r="R7" t="n">
-        <v>6660481</v>
+        <v>6660713</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121354210</v>
+        <v>121354241</v>
       </c>
       <c r="B8" t="n">
-        <v>98049</v>
+        <v>100256</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696874</v>
+        <v>696825</v>
       </c>
       <c r="R8" t="n">
-        <v>6660666</v>
+        <v>6660796</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121354226</v>
+        <v>121354251</v>
       </c>
       <c r="B9" t="n">
-        <v>98049</v>
+        <v>90131</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,21 +1496,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>4191</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Geastrum michelianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Berk. &amp; Broome</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696779</v>
+        <v>696840</v>
       </c>
       <c r="R9" t="n">
-        <v>6660917</v>
+        <v>6660674</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121354158</v>
+        <v>121354234</v>
       </c>
       <c r="B10" t="n">
-        <v>98049</v>
+        <v>100256</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,21 +1611,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696777</v>
+        <v>696786</v>
       </c>
       <c r="R10" t="n">
-        <v>6660623</v>
+        <v>6660804</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,12 +1674,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121354216</v>
+        <v>121354199</v>
       </c>
       <c r="B11" t="n">
-        <v>91620</v>
+        <v>100256</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1726,21 +1726,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>696818</v>
+        <v>696837</v>
       </c>
       <c r="R11" t="n">
-        <v>6660846</v>
+        <v>6660782</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121354258</v>
+        <v>121354256</v>
       </c>
       <c r="B12" t="n">
-        <v>103585</v>
+        <v>100256</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,16 +1841,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222412</v>
+        <v>222771</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696953</v>
+        <v>696843</v>
       </c>
       <c r="R12" t="n">
-        <v>6660737</v>
+        <v>6660663</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121354230</v>
+        <v>121354267</v>
       </c>
       <c r="B13" t="n">
-        <v>98049</v>
+        <v>100256</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696816</v>
+        <v>696878</v>
       </c>
       <c r="R13" t="n">
-        <v>6660877</v>
+        <v>6660770</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2055,10 +2055,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121354154</v>
+        <v>121354208</v>
       </c>
       <c r="B14" t="n">
-        <v>100337</v>
+        <v>100256</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,21 +2071,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696874</v>
+        <v>696843</v>
       </c>
       <c r="R14" t="n">
-        <v>6660583</v>
+        <v>6660799</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2170,10 +2170,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121354256</v>
+        <v>121354239</v>
       </c>
       <c r="B15" t="n">
-        <v>100246</v>
+        <v>100256</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696843</v>
+        <v>696830</v>
       </c>
       <c r="R15" t="n">
-        <v>6660663</v>
+        <v>6660785</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121354228</v>
+        <v>121354265</v>
       </c>
       <c r="B16" t="n">
-        <v>91620</v>
+        <v>100256</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,21 +2301,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696786</v>
+        <v>696849</v>
       </c>
       <c r="R16" t="n">
-        <v>6660910</v>
+        <v>6660766</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2400,10 +2400,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121354206</v>
+        <v>121354156</v>
       </c>
       <c r="B17" t="n">
-        <v>98049</v>
+        <v>100347</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2416,21 +2416,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696910</v>
+        <v>696718</v>
       </c>
       <c r="R17" t="n">
-        <v>6660863</v>
+        <v>6660612</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2515,10 +2515,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121354199</v>
+        <v>121354210</v>
       </c>
       <c r="B18" t="n">
-        <v>100246</v>
+        <v>98059</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2531,21 +2531,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696837</v>
+        <v>696874</v>
       </c>
       <c r="R18" t="n">
-        <v>6660782</v>
+        <v>6660666</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2630,10 +2630,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121354165</v>
+        <v>121354230</v>
       </c>
       <c r="B19" t="n">
-        <v>100337</v>
+        <v>98059</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2646,21 +2646,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696683</v>
+        <v>696816</v>
       </c>
       <c r="R19" t="n">
-        <v>6660536</v>
+        <v>6660877</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2709,12 +2709,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2745,10 +2745,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121354237</v>
+        <v>121354226</v>
       </c>
       <c r="B20" t="n">
-        <v>100246</v>
+        <v>98059</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2761,21 +2761,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696816</v>
+        <v>696779</v>
       </c>
       <c r="R20" t="n">
-        <v>6660789</v>
+        <v>6660917</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2860,10 +2860,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121354202</v>
+        <v>121354158</v>
       </c>
       <c r="B21" t="n">
-        <v>100246</v>
+        <v>98059</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696939</v>
+        <v>696777</v>
       </c>
       <c r="R21" t="n">
-        <v>6660882</v>
+        <v>6660623</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2975,10 +2975,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121354213</v>
+        <v>121354258</v>
       </c>
       <c r="B22" t="n">
-        <v>100246</v>
+        <v>103595</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2991,16 +2991,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696829</v>
+        <v>696953</v>
       </c>
       <c r="R22" t="n">
-        <v>6660866</v>
+        <v>6660737</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3090,10 +3090,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121354223</v>
+        <v>121354154</v>
       </c>
       <c r="B23" t="n">
-        <v>100246</v>
+        <v>100347</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3106,21 +3106,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696708</v>
+        <v>696874</v>
       </c>
       <c r="R23" t="n">
-        <v>6660830</v>
+        <v>6660583</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3169,12 +3169,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3205,10 +3205,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121354156</v>
+        <v>121354165</v>
       </c>
       <c r="B24" t="n">
-        <v>100337</v>
+        <v>100347</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696718</v>
+        <v>696683</v>
       </c>
       <c r="R24" t="n">
-        <v>6660612</v>
+        <v>6660536</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3320,10 +3320,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121354267</v>
+        <v>121354249</v>
       </c>
       <c r="B25" t="n">
-        <v>100246</v>
+        <v>100256</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696878</v>
+        <v>696815</v>
       </c>
       <c r="R25" t="n">
-        <v>6660770</v>
+        <v>6660731</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3435,10 +3435,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121354208</v>
+        <v>121354152</v>
       </c>
       <c r="B26" t="n">
-        <v>100246</v>
+        <v>91630</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3451,21 +3451,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696843</v>
+        <v>696860</v>
       </c>
       <c r="R26" t="n">
-        <v>6660799</v>
+        <v>6660584</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3550,10 +3550,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121354141</v>
+        <v>121354143</v>
       </c>
       <c r="B27" t="n">
-        <v>101240</v>
+        <v>100347</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3566,21 +3566,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696745</v>
+        <v>696882</v>
       </c>
       <c r="R27" t="n">
-        <v>6660466</v>
+        <v>6660480</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3665,10 +3665,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121354265</v>
+        <v>121354245</v>
       </c>
       <c r="B28" t="n">
-        <v>100246</v>
+        <v>100256</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696849</v>
+        <v>696963</v>
       </c>
       <c r="R28" t="n">
-        <v>6660766</v>
+        <v>6660755</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3780,10 +3780,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121354245</v>
+        <v>121354141</v>
       </c>
       <c r="B29" t="n">
-        <v>100246</v>
+        <v>101250</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3796,21 +3796,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696963</v>
+        <v>696745</v>
       </c>
       <c r="R29" t="n">
-        <v>6660755</v>
+        <v>6660466</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3859,12 +3859,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3895,10 +3895,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121354247</v>
+        <v>121354148</v>
       </c>
       <c r="B30" t="n">
-        <v>100246</v>
+        <v>101250</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3911,21 +3911,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3944,10 +3944,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696845</v>
+        <v>696853</v>
       </c>
       <c r="R30" t="n">
-        <v>6660742</v>
+        <v>6660481</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3974,12 +3974,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4010,10 +4010,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121354234</v>
+        <v>121354204</v>
       </c>
       <c r="B31" t="n">
-        <v>100246</v>
+        <v>98059</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4026,21 +4026,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>696786</v>
+        <v>696959</v>
       </c>
       <c r="R31" t="n">
-        <v>6660804</v>
+        <v>6660847</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4089,12 +4089,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4125,10 +4125,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121354204</v>
+        <v>121354228</v>
       </c>
       <c r="B32" t="n">
-        <v>98049</v>
+        <v>91630</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4141,21 +4141,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696959</v>
+        <v>696786</v>
       </c>
       <c r="R32" t="n">
-        <v>6660847</v>
+        <v>6660910</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4204,12 +4204,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4240,10 +4240,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121354218</v>
+        <v>121354223</v>
       </c>
       <c r="B33" t="n">
-        <v>100246</v>
+        <v>100256</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4289,10 +4289,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696810</v>
+        <v>696708</v>
       </c>
       <c r="R33" t="n">
-        <v>6660842</v>
+        <v>6660830</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4355,10 +4355,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121354239</v>
+        <v>121354213</v>
       </c>
       <c r="B34" t="n">
-        <v>100246</v>
+        <v>100256</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4404,10 +4404,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696830</v>
+        <v>696829</v>
       </c>
       <c r="R34" t="n">
-        <v>6660785</v>
+        <v>6660866</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4470,10 +4470,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121354143</v>
+        <v>121354237</v>
       </c>
       <c r="B35" t="n">
-        <v>100337</v>
+        <v>100256</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4486,21 +4486,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4519,10 +4519,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696882</v>
+        <v>696816</v>
       </c>
       <c r="R35" t="n">
-        <v>6660480</v>
+        <v>6660789</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4549,12 +4549,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 48490-2022 artfynd.xlsx
+++ b/artfynd/A 48490-2022 artfynd.xlsx
@@ -3205,10 +3205,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121354165</v>
+        <v>121354249</v>
       </c>
       <c r="B24" t="n">
-        <v>100347</v>
+        <v>100256</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3221,21 +3221,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696683</v>
+        <v>696815</v>
       </c>
       <c r="R24" t="n">
-        <v>6660536</v>
+        <v>6660731</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3284,12 +3284,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3320,10 +3320,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121354249</v>
+        <v>121354165</v>
       </c>
       <c r="B25" t="n">
-        <v>100256</v>
+        <v>100347</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3336,21 +3336,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696815</v>
+        <v>696683</v>
       </c>
       <c r="R25" t="n">
-        <v>6660731</v>
+        <v>6660536</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3399,12 +3399,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 48490-2022 artfynd.xlsx
+++ b/artfynd/A 48490-2022 artfynd.xlsx
@@ -3205,10 +3205,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121354249</v>
+        <v>121354165</v>
       </c>
       <c r="B24" t="n">
-        <v>100256</v>
+        <v>100347</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3221,21 +3221,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696815</v>
+        <v>696683</v>
       </c>
       <c r="R24" t="n">
-        <v>6660731</v>
+        <v>6660536</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3284,12 +3284,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3320,10 +3320,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121354165</v>
+        <v>121354249</v>
       </c>
       <c r="B25" t="n">
-        <v>100347</v>
+        <v>100256</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3336,21 +3336,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696683</v>
+        <v>696815</v>
       </c>
       <c r="R25" t="n">
-        <v>6660536</v>
+        <v>6660731</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3399,12 +3399,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 48490-2022 artfynd.xlsx
+++ b/artfynd/A 48490-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121354216</v>
+        <v>121354206</v>
       </c>
       <c r="B2" t="n">
-        <v>91630</v>
+        <v>98059</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>696818</v>
+        <v>696910</v>
       </c>
       <c r="R2" t="n">
-        <v>6660846</v>
+        <v>6660863</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121354206</v>
+        <v>121354213</v>
       </c>
       <c r="B3" t="n">
-        <v>98059</v>
+        <v>100256</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>696910</v>
+        <v>696829</v>
       </c>
       <c r="R3" t="n">
-        <v>6660863</v>
+        <v>6660866</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121354218</v>
+        <v>121354245</v>
       </c>
       <c r="B4" t="n">
         <v>100256</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>696810</v>
+        <v>696963</v>
       </c>
       <c r="R4" t="n">
-        <v>6660842</v>
+        <v>6660755</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121354202</v>
+        <v>121354165</v>
       </c>
       <c r="B5" t="n">
-        <v>100256</v>
+        <v>100347</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696939</v>
+        <v>696683</v>
       </c>
       <c r="R5" t="n">
-        <v>6660882</v>
+        <v>6660536</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,7 +1135,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121354247</v>
+        <v>121354265</v>
       </c>
       <c r="B6" t="n">
         <v>100256</v>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696845</v>
+        <v>696849</v>
       </c>
       <c r="R6" t="n">
-        <v>6660742</v>
+        <v>6660766</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121354254</v>
+        <v>121354223</v>
       </c>
       <c r="B7" t="n">
         <v>100256</v>
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696815</v>
+        <v>696708</v>
       </c>
       <c r="R7" t="n">
-        <v>6660713</v>
+        <v>6660830</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121354241</v>
+        <v>121354249</v>
       </c>
       <c r="B8" t="n">
         <v>100256</v>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696825</v>
+        <v>696815</v>
       </c>
       <c r="R8" t="n">
-        <v>6660796</v>
+        <v>6660731</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121354234</v>
+        <v>121354228</v>
       </c>
       <c r="B10" t="n">
-        <v>100256</v>
+        <v>91630</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,21 +1611,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1647,7 +1647,7 @@
         <v>696786</v>
       </c>
       <c r="R10" t="n">
-        <v>6660804</v>
+        <v>6660910</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,7 +1710,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121354199</v>
+        <v>121354254</v>
       </c>
       <c r="B11" t="n">
         <v>100256</v>
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>696837</v>
+        <v>696815</v>
       </c>
       <c r="R11" t="n">
-        <v>6660782</v>
+        <v>6660713</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121354256</v>
+        <v>121354156</v>
       </c>
       <c r="B12" t="n">
-        <v>100256</v>
+        <v>100347</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,21 +1841,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696843</v>
+        <v>696718</v>
       </c>
       <c r="R12" t="n">
-        <v>6660663</v>
+        <v>6660612</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1904,12 +1904,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,10 +1940,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121354267</v>
+        <v>121354226</v>
       </c>
       <c r="B13" t="n">
-        <v>100256</v>
+        <v>98059</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696878</v>
+        <v>696779</v>
       </c>
       <c r="R13" t="n">
-        <v>6660770</v>
+        <v>6660917</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121354208</v>
+        <v>121354199</v>
       </c>
       <c r="B14" t="n">
         <v>100256</v>
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696843</v>
+        <v>696837</v>
       </c>
       <c r="R14" t="n">
-        <v>6660799</v>
+        <v>6660782</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2170,10 +2170,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121354239</v>
+        <v>121354148</v>
       </c>
       <c r="B15" t="n">
-        <v>100256</v>
+        <v>101250</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2186,21 +2186,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696830</v>
+        <v>696853</v>
       </c>
       <c r="R15" t="n">
-        <v>6660785</v>
+        <v>6660481</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2249,12 +2249,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121354265</v>
+        <v>121354204</v>
       </c>
       <c r="B16" t="n">
-        <v>100256</v>
+        <v>98059</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,21 +2301,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696849</v>
+        <v>696959</v>
       </c>
       <c r="R16" t="n">
-        <v>6660766</v>
+        <v>6660847</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2400,10 +2400,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121354156</v>
+        <v>121354216</v>
       </c>
       <c r="B17" t="n">
-        <v>100347</v>
+        <v>91630</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2416,21 +2416,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696718</v>
+        <v>696818</v>
       </c>
       <c r="R17" t="n">
-        <v>6660612</v>
+        <v>6660846</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2479,12 +2479,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2515,10 +2515,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121354210</v>
+        <v>121354218</v>
       </c>
       <c r="B18" t="n">
-        <v>98059</v>
+        <v>100256</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2531,21 +2531,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696874</v>
+        <v>696810</v>
       </c>
       <c r="R18" t="n">
-        <v>6660666</v>
+        <v>6660842</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2594,12 +2594,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2630,10 +2630,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121354230</v>
+        <v>121354239</v>
       </c>
       <c r="B19" t="n">
-        <v>98059</v>
+        <v>100256</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2646,21 +2646,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696816</v>
+        <v>696830</v>
       </c>
       <c r="R19" t="n">
-        <v>6660877</v>
+        <v>6660785</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2745,10 +2745,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121354226</v>
+        <v>121354141</v>
       </c>
       <c r="B20" t="n">
-        <v>98059</v>
+        <v>101250</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2761,21 +2761,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219798</v>
+        <v>221235</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696779</v>
+        <v>696745</v>
       </c>
       <c r="R20" t="n">
-        <v>6660917</v>
+        <v>6660466</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2824,12 +2824,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2860,10 +2860,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121354158</v>
+        <v>121354258</v>
       </c>
       <c r="B21" t="n">
-        <v>98059</v>
+        <v>103595</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219798</v>
+        <v>222412</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696777</v>
+        <v>696953</v>
       </c>
       <c r="R21" t="n">
-        <v>6660623</v>
+        <v>6660737</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2939,12 +2939,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2975,10 +2975,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121354258</v>
+        <v>121354208</v>
       </c>
       <c r="B22" t="n">
-        <v>103595</v>
+        <v>100256</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2991,16 +2991,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222412</v>
+        <v>222771</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696953</v>
+        <v>696843</v>
       </c>
       <c r="R22" t="n">
-        <v>6660737</v>
+        <v>6660799</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3054,12 +3054,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3090,10 +3090,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121354154</v>
+        <v>121354234</v>
       </c>
       <c r="B23" t="n">
-        <v>100347</v>
+        <v>100256</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3106,21 +3106,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696874</v>
+        <v>696786</v>
       </c>
       <c r="R23" t="n">
-        <v>6660583</v>
+        <v>6660804</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3169,12 +3169,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3205,10 +3205,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121354165</v>
+        <v>121354237</v>
       </c>
       <c r="B24" t="n">
-        <v>100347</v>
+        <v>100256</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3221,21 +3221,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696683</v>
+        <v>696816</v>
       </c>
       <c r="R24" t="n">
-        <v>6660536</v>
+        <v>6660789</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3284,12 +3284,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3320,10 +3320,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121354249</v>
+        <v>121354152</v>
       </c>
       <c r="B25" t="n">
-        <v>100256</v>
+        <v>91630</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3336,21 +3336,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696815</v>
+        <v>696860</v>
       </c>
       <c r="R25" t="n">
-        <v>6660731</v>
+        <v>6660584</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3399,12 +3399,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3435,10 +3435,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121354152</v>
+        <v>121354154</v>
       </c>
       <c r="B26" t="n">
-        <v>91630</v>
+        <v>100347</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3451,21 +3451,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696860</v>
+        <v>696874</v>
       </c>
       <c r="R26" t="n">
-        <v>6660584</v>
+        <v>6660583</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3550,10 +3550,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121354143</v>
+        <v>121354210</v>
       </c>
       <c r="B27" t="n">
-        <v>100347</v>
+        <v>98059</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3566,21 +3566,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696882</v>
+        <v>696874</v>
       </c>
       <c r="R27" t="n">
-        <v>6660480</v>
+        <v>6660666</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3665,7 +3665,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121354245</v>
+        <v>121354241</v>
       </c>
       <c r="B28" t="n">
         <v>100256</v>
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696963</v>
+        <v>696825</v>
       </c>
       <c r="R28" t="n">
-        <v>6660755</v>
+        <v>6660796</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3780,10 +3780,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121354141</v>
+        <v>121354267</v>
       </c>
       <c r="B29" t="n">
-        <v>101250</v>
+        <v>100256</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3796,21 +3796,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696745</v>
+        <v>696878</v>
       </c>
       <c r="R29" t="n">
-        <v>6660466</v>
+        <v>6660770</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3859,12 +3859,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3895,10 +3895,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121354148</v>
+        <v>121354158</v>
       </c>
       <c r="B30" t="n">
-        <v>101250</v>
+        <v>98059</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3911,21 +3911,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221235</v>
+        <v>219798</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3944,10 +3944,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696853</v>
+        <v>696777</v>
       </c>
       <c r="R30" t="n">
-        <v>6660481</v>
+        <v>6660623</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4010,10 +4010,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121354204</v>
+        <v>121354247</v>
       </c>
       <c r="B31" t="n">
-        <v>98059</v>
+        <v>100256</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4026,21 +4026,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>696959</v>
+        <v>696845</v>
       </c>
       <c r="R31" t="n">
-        <v>6660847</v>
+        <v>6660742</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4089,12 +4089,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4125,10 +4125,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121354228</v>
+        <v>121354143</v>
       </c>
       <c r="B32" t="n">
-        <v>91630</v>
+        <v>100347</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4141,21 +4141,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696786</v>
+        <v>696882</v>
       </c>
       <c r="R32" t="n">
-        <v>6660910</v>
+        <v>6660480</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4204,12 +4204,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4240,10 +4240,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121354223</v>
+        <v>121354230</v>
       </c>
       <c r="B33" t="n">
-        <v>100256</v>
+        <v>98059</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4256,21 +4256,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4289,10 +4289,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696708</v>
+        <v>696816</v>
       </c>
       <c r="R33" t="n">
-        <v>6660830</v>
+        <v>6660877</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4355,7 +4355,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121354213</v>
+        <v>121354256</v>
       </c>
       <c r="B34" t="n">
         <v>100256</v>
@@ -4404,10 +4404,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696829</v>
+        <v>696843</v>
       </c>
       <c r="R34" t="n">
-        <v>6660866</v>
+        <v>6660663</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4470,7 +4470,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121354237</v>
+        <v>121354202</v>
       </c>
       <c r="B35" t="n">
         <v>100256</v>
@@ -4519,10 +4519,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696816</v>
+        <v>696939</v>
       </c>
       <c r="R35" t="n">
-        <v>6660789</v>
+        <v>6660882</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4549,12 +4549,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 48490-2022 artfynd.xlsx
+++ b/artfynd/A 48490-2022 artfynd.xlsx
@@ -2170,10 +2170,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121354148</v>
+        <v>121354204</v>
       </c>
       <c r="B15" t="n">
-        <v>101250</v>
+        <v>98059</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2186,21 +2186,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221235</v>
+        <v>219798</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696853</v>
+        <v>696959</v>
       </c>
       <c r="R15" t="n">
-        <v>6660481</v>
+        <v>6660847</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121354204</v>
+        <v>121354148</v>
       </c>
       <c r="B16" t="n">
-        <v>98059</v>
+        <v>101250</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,21 +2301,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219798</v>
+        <v>221235</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696959</v>
+        <v>696853</v>
       </c>
       <c r="R16" t="n">
-        <v>6660847</v>
+        <v>6660481</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2745,10 +2745,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121354141</v>
+        <v>121354208</v>
       </c>
       <c r="B20" t="n">
-        <v>101250</v>
+        <v>100256</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2761,21 +2761,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696745</v>
+        <v>696843</v>
       </c>
       <c r="R20" t="n">
-        <v>6660466</v>
+        <v>6660799</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2860,10 +2860,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121354258</v>
+        <v>121354141</v>
       </c>
       <c r="B21" t="n">
-        <v>103595</v>
+        <v>101250</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696953</v>
+        <v>696745</v>
       </c>
       <c r="R21" t="n">
-        <v>6660737</v>
+        <v>6660466</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2939,12 +2939,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2975,10 +2975,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121354208</v>
+        <v>121354258</v>
       </c>
       <c r="B22" t="n">
-        <v>100256</v>
+        <v>103595</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2991,16 +2991,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696843</v>
+        <v>696953</v>
       </c>
       <c r="R22" t="n">
-        <v>6660799</v>
+        <v>6660737</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3054,12 +3054,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 48490-2022 artfynd.xlsx
+++ b/artfynd/A 48490-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121354206</v>
+        <v>121354251</v>
       </c>
       <c r="B2" t="n">
-        <v>98059</v>
+        <v>90139</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>4191</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Geastrum michelianum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Berk. &amp; Broome</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>696910</v>
+        <v>696840</v>
       </c>
       <c r="R2" t="n">
-        <v>6660863</v>
+        <v>6660674</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121354213</v>
+        <v>121354141</v>
       </c>
       <c r="B3" t="n">
-        <v>100256</v>
+        <v>101263</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>696829</v>
+        <v>696745</v>
       </c>
       <c r="R3" t="n">
-        <v>6660866</v>
+        <v>6660466</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121354245</v>
+        <v>121354148</v>
       </c>
       <c r="B4" t="n">
-        <v>100256</v>
+        <v>101263</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,21 +921,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>696963</v>
+        <v>696853</v>
       </c>
       <c r="R4" t="n">
-        <v>6660755</v>
+        <v>6660481</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,12 +984,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121354165</v>
+        <v>121354265</v>
       </c>
       <c r="B5" t="n">
-        <v>100347</v>
+        <v>100269</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696683</v>
+        <v>696849</v>
       </c>
       <c r="R5" t="n">
-        <v>6660536</v>
+        <v>6660766</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121354265</v>
+        <v>121354216</v>
       </c>
       <c r="B6" t="n">
-        <v>100256</v>
+        <v>91642</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,21 +1151,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696849</v>
+        <v>696818</v>
       </c>
       <c r="R6" t="n">
-        <v>6660766</v>
+        <v>6660846</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121354223</v>
+        <v>121354158</v>
       </c>
       <c r="B7" t="n">
-        <v>100256</v>
+        <v>98072</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696708</v>
+        <v>696777</v>
       </c>
       <c r="R7" t="n">
-        <v>6660830</v>
+        <v>6660623</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121354249</v>
+        <v>121354154</v>
       </c>
       <c r="B8" t="n">
-        <v>100256</v>
+        <v>100360</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696815</v>
+        <v>696874</v>
       </c>
       <c r="R8" t="n">
-        <v>6660731</v>
+        <v>6660583</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121354251</v>
+        <v>121354239</v>
       </c>
       <c r="B9" t="n">
-        <v>90131</v>
+        <v>100269</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,21 +1496,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4191</v>
+        <v>222771</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Geastrum michelianum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Berk. &amp; Broome</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696840</v>
+        <v>696830</v>
       </c>
       <c r="R9" t="n">
-        <v>6660674</v>
+        <v>6660785</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121354228</v>
+        <v>121354247</v>
       </c>
       <c r="B10" t="n">
-        <v>91630</v>
+        <v>100269</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,21 +1611,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696786</v>
+        <v>696845</v>
       </c>
       <c r="R10" t="n">
-        <v>6660910</v>
+        <v>6660742</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121354254</v>
+        <v>121354267</v>
       </c>
       <c r="B11" t="n">
-        <v>100256</v>
+        <v>100269</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>696815</v>
+        <v>696878</v>
       </c>
       <c r="R11" t="n">
-        <v>6660713</v>
+        <v>6660770</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121354156</v>
+        <v>121354226</v>
       </c>
       <c r="B12" t="n">
-        <v>100347</v>
+        <v>98072</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,21 +1841,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696718</v>
+        <v>696779</v>
       </c>
       <c r="R12" t="n">
-        <v>6660612</v>
+        <v>6660917</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1904,12 +1904,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,10 +1940,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121354226</v>
+        <v>121354204</v>
       </c>
       <c r="B13" t="n">
-        <v>98059</v>
+        <v>98072</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696779</v>
+        <v>696959</v>
       </c>
       <c r="R13" t="n">
-        <v>6660917</v>
+        <v>6660847</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,12 +2019,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2055,10 +2055,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121354199</v>
+        <v>121354258</v>
       </c>
       <c r="B14" t="n">
-        <v>100256</v>
+        <v>103608</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,16 +2071,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696837</v>
+        <v>696953</v>
       </c>
       <c r="R14" t="n">
-        <v>6660782</v>
+        <v>6660737</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,10 +2170,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121354204</v>
+        <v>121354234</v>
       </c>
       <c r="B15" t="n">
-        <v>98059</v>
+        <v>100269</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2186,21 +2186,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696959</v>
+        <v>696786</v>
       </c>
       <c r="R15" t="n">
-        <v>6660847</v>
+        <v>6660804</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2249,12 +2249,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121354148</v>
+        <v>121354228</v>
       </c>
       <c r="B16" t="n">
-        <v>101250</v>
+        <v>91642</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,21 +2301,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221235</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696853</v>
+        <v>696786</v>
       </c>
       <c r="R16" t="n">
-        <v>6660481</v>
+        <v>6660910</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2400,10 +2400,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121354216</v>
+        <v>121354223</v>
       </c>
       <c r="B17" t="n">
-        <v>91630</v>
+        <v>100269</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2416,21 +2416,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696818</v>
+        <v>696708</v>
       </c>
       <c r="R17" t="n">
-        <v>6660846</v>
+        <v>6660830</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2515,10 +2515,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121354218</v>
+        <v>121354199</v>
       </c>
       <c r="B18" t="n">
-        <v>100256</v>
+        <v>100269</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696810</v>
+        <v>696837</v>
       </c>
       <c r="R18" t="n">
-        <v>6660842</v>
+        <v>6660782</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2594,12 +2594,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2630,10 +2630,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121354239</v>
+        <v>121354208</v>
       </c>
       <c r="B19" t="n">
-        <v>100256</v>
+        <v>100269</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696830</v>
+        <v>696843</v>
       </c>
       <c r="R19" t="n">
-        <v>6660785</v>
+        <v>6660799</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2709,12 +2709,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2745,10 +2745,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121354208</v>
+        <v>121354213</v>
       </c>
       <c r="B20" t="n">
-        <v>100256</v>
+        <v>100269</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696843</v>
+        <v>696829</v>
       </c>
       <c r="R20" t="n">
-        <v>6660799</v>
+        <v>6660866</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2824,12 +2824,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2860,10 +2860,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121354141</v>
+        <v>121354245</v>
       </c>
       <c r="B21" t="n">
-        <v>101250</v>
+        <v>100269</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696745</v>
+        <v>696963</v>
       </c>
       <c r="R21" t="n">
-        <v>6660466</v>
+        <v>6660755</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2939,12 +2939,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2975,10 +2975,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121354258</v>
+        <v>121354256</v>
       </c>
       <c r="B22" t="n">
-        <v>103595</v>
+        <v>100269</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2991,16 +2991,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222412</v>
+        <v>222771</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696953</v>
+        <v>696843</v>
       </c>
       <c r="R22" t="n">
-        <v>6660737</v>
+        <v>6660663</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3090,10 +3090,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121354234</v>
+        <v>121354218</v>
       </c>
       <c r="B23" t="n">
-        <v>100256</v>
+        <v>100269</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696786</v>
+        <v>696810</v>
       </c>
       <c r="R23" t="n">
-        <v>6660804</v>
+        <v>6660842</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3205,10 +3205,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121354237</v>
+        <v>121354241</v>
       </c>
       <c r="B24" t="n">
-        <v>100256</v>
+        <v>100269</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696816</v>
+        <v>696825</v>
       </c>
       <c r="R24" t="n">
-        <v>6660789</v>
+        <v>6660796</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3320,10 +3320,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121354152</v>
+        <v>121354202</v>
       </c>
       <c r="B25" t="n">
-        <v>91630</v>
+        <v>100269</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3336,21 +3336,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696860</v>
+        <v>696939</v>
       </c>
       <c r="R25" t="n">
-        <v>6660584</v>
+        <v>6660882</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3435,10 +3435,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121354154</v>
+        <v>121354156</v>
       </c>
       <c r="B26" t="n">
-        <v>100347</v>
+        <v>100360</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696874</v>
+        <v>696718</v>
       </c>
       <c r="R26" t="n">
-        <v>6660583</v>
+        <v>6660612</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3550,10 +3550,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121354210</v>
+        <v>121354165</v>
       </c>
       <c r="B27" t="n">
-        <v>98059</v>
+        <v>100360</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3566,21 +3566,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696874</v>
+        <v>696683</v>
       </c>
       <c r="R27" t="n">
-        <v>6660666</v>
+        <v>6660536</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3665,10 +3665,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121354241</v>
+        <v>121354237</v>
       </c>
       <c r="B28" t="n">
-        <v>100256</v>
+        <v>100269</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696825</v>
+        <v>696816</v>
       </c>
       <c r="R28" t="n">
-        <v>6660796</v>
+        <v>6660789</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3780,10 +3780,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121354267</v>
+        <v>121354152</v>
       </c>
       <c r="B29" t="n">
-        <v>100256</v>
+        <v>91642</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3796,21 +3796,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696878</v>
+        <v>696860</v>
       </c>
       <c r="R29" t="n">
-        <v>6660770</v>
+        <v>6660584</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3859,12 +3859,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3895,10 +3895,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121354158</v>
+        <v>121354206</v>
       </c>
       <c r="B30" t="n">
-        <v>98059</v>
+        <v>98072</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3944,10 +3944,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696777</v>
+        <v>696910</v>
       </c>
       <c r="R30" t="n">
-        <v>6660623</v>
+        <v>6660863</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4010,10 +4010,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121354247</v>
+        <v>121354210</v>
       </c>
       <c r="B31" t="n">
-        <v>100256</v>
+        <v>98072</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4026,21 +4026,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>696845</v>
+        <v>696874</v>
       </c>
       <c r="R31" t="n">
-        <v>6660742</v>
+        <v>6660666</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4089,12 +4089,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4125,10 +4125,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121354143</v>
+        <v>121354230</v>
       </c>
       <c r="B32" t="n">
-        <v>100347</v>
+        <v>98072</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4141,21 +4141,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696882</v>
+        <v>696816</v>
       </c>
       <c r="R32" t="n">
-        <v>6660480</v>
+        <v>6660877</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4204,12 +4204,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4240,10 +4240,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121354230</v>
+        <v>121354249</v>
       </c>
       <c r="B33" t="n">
-        <v>98059</v>
+        <v>100269</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4256,21 +4256,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4289,10 +4289,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696816</v>
+        <v>696815</v>
       </c>
       <c r="R33" t="n">
-        <v>6660877</v>
+        <v>6660731</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4355,10 +4355,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121354256</v>
+        <v>121354254</v>
       </c>
       <c r="B34" t="n">
-        <v>100256</v>
+        <v>100269</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4404,10 +4404,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696843</v>
+        <v>696815</v>
       </c>
       <c r="R34" t="n">
-        <v>6660663</v>
+        <v>6660713</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4470,10 +4470,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121354202</v>
+        <v>121354143</v>
       </c>
       <c r="B35" t="n">
-        <v>100256</v>
+        <v>100360</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4486,21 +4486,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4519,10 +4519,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696939</v>
+        <v>696882</v>
       </c>
       <c r="R35" t="n">
-        <v>6660882</v>
+        <v>6660480</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 48490-2022 artfynd.xlsx
+++ b/artfynd/A 48490-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121354251</v>
+        <v>121354218</v>
       </c>
       <c r="B2" t="n">
-        <v>90139</v>
+        <v>100270</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4191</v>
+        <v>222771</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Geastrum michelianum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Berk. &amp; Broome</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>696840</v>
+        <v>696810</v>
       </c>
       <c r="R2" t="n">
-        <v>6660674</v>
+        <v>6660842</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121354141</v>
+        <v>121354234</v>
       </c>
       <c r="B3" t="n">
-        <v>101263</v>
+        <v>100270</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>696745</v>
+        <v>696786</v>
       </c>
       <c r="R3" t="n">
-        <v>6660466</v>
+        <v>6660804</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121354148</v>
+        <v>121354141</v>
       </c>
       <c r="B4" t="n">
-        <v>101263</v>
+        <v>101264</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>696853</v>
+        <v>696745</v>
       </c>
       <c r="R4" t="n">
-        <v>6660481</v>
+        <v>6660466</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121354265</v>
+        <v>121354206</v>
       </c>
       <c r="B5" t="n">
-        <v>100269</v>
+        <v>98073</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696849</v>
+        <v>696910</v>
       </c>
       <c r="R5" t="n">
-        <v>6660766</v>
+        <v>6660863</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121354216</v>
+        <v>121354237</v>
       </c>
       <c r="B6" t="n">
-        <v>91642</v>
+        <v>100270</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,21 +1151,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696818</v>
+        <v>696816</v>
       </c>
       <c r="R6" t="n">
-        <v>6660846</v>
+        <v>6660789</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121354158</v>
+        <v>121354154</v>
       </c>
       <c r="B7" t="n">
-        <v>98072</v>
+        <v>100361</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696777</v>
+        <v>696874</v>
       </c>
       <c r="R7" t="n">
-        <v>6660623</v>
+        <v>6660583</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121354154</v>
+        <v>121354223</v>
       </c>
       <c r="B8" t="n">
-        <v>100360</v>
+        <v>100270</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696874</v>
+        <v>696708</v>
       </c>
       <c r="R8" t="n">
-        <v>6660583</v>
+        <v>6660830</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121354239</v>
+        <v>121354256</v>
       </c>
       <c r="B9" t="n">
-        <v>100269</v>
+        <v>100270</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696830</v>
+        <v>696843</v>
       </c>
       <c r="R9" t="n">
-        <v>6660785</v>
+        <v>6660663</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121354247</v>
+        <v>121354230</v>
       </c>
       <c r="B10" t="n">
-        <v>100269</v>
+        <v>98073</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,21 +1611,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696845</v>
+        <v>696816</v>
       </c>
       <c r="R10" t="n">
-        <v>6660742</v>
+        <v>6660877</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121354267</v>
+        <v>121354158</v>
       </c>
       <c r="B11" t="n">
-        <v>100269</v>
+        <v>98073</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1726,21 +1726,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>696878</v>
+        <v>696777</v>
       </c>
       <c r="R11" t="n">
-        <v>6660770</v>
+        <v>6660623</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121354226</v>
+        <v>121354251</v>
       </c>
       <c r="B12" t="n">
-        <v>98072</v>
+        <v>90140</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,21 +1841,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219798</v>
+        <v>4191</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Geastrum michelianum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Berk. &amp; Broome</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696779</v>
+        <v>696840</v>
       </c>
       <c r="R12" t="n">
-        <v>6660917</v>
+        <v>6660674</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121354204</v>
+        <v>121354156</v>
       </c>
       <c r="B13" t="n">
-        <v>98072</v>
+        <v>100361</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696959</v>
+        <v>696718</v>
       </c>
       <c r="R13" t="n">
-        <v>6660847</v>
+        <v>6660612</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2055,10 +2055,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121354258</v>
+        <v>121354265</v>
       </c>
       <c r="B14" t="n">
-        <v>103608</v>
+        <v>100270</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,16 +2071,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222412</v>
+        <v>222771</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696953</v>
+        <v>696849</v>
       </c>
       <c r="R14" t="n">
-        <v>6660737</v>
+        <v>6660766</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2170,10 +2170,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121354234</v>
+        <v>121354267</v>
       </c>
       <c r="B15" t="n">
-        <v>100269</v>
+        <v>100270</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696786</v>
+        <v>696878</v>
       </c>
       <c r="R15" t="n">
-        <v>6660804</v>
+        <v>6660770</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121354228</v>
+        <v>121354204</v>
       </c>
       <c r="B16" t="n">
-        <v>91642</v>
+        <v>98073</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,21 +2301,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696786</v>
+        <v>696959</v>
       </c>
       <c r="R16" t="n">
-        <v>6660910</v>
+        <v>6660847</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2400,10 +2400,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121354223</v>
+        <v>121354254</v>
       </c>
       <c r="B17" t="n">
-        <v>100269</v>
+        <v>100270</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696708</v>
+        <v>696815</v>
       </c>
       <c r="R17" t="n">
-        <v>6660830</v>
+        <v>6660713</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2515,10 +2515,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121354199</v>
+        <v>121354143</v>
       </c>
       <c r="B18" t="n">
-        <v>100269</v>
+        <v>100361</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2531,21 +2531,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696837</v>
+        <v>696882</v>
       </c>
       <c r="R18" t="n">
-        <v>6660782</v>
+        <v>6660480</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2630,10 +2630,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121354208</v>
+        <v>121354152</v>
       </c>
       <c r="B19" t="n">
-        <v>100269</v>
+        <v>91643</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2646,21 +2646,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696843</v>
+        <v>696860</v>
       </c>
       <c r="R19" t="n">
-        <v>6660799</v>
+        <v>6660584</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2745,10 +2745,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121354213</v>
+        <v>121354216</v>
       </c>
       <c r="B20" t="n">
-        <v>100269</v>
+        <v>91643</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2761,21 +2761,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696829</v>
+        <v>696818</v>
       </c>
       <c r="R20" t="n">
-        <v>6660866</v>
+        <v>6660846</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2860,10 +2860,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121354245</v>
+        <v>121354148</v>
       </c>
       <c r="B21" t="n">
-        <v>100269</v>
+        <v>101264</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696963</v>
+        <v>696853</v>
       </c>
       <c r="R21" t="n">
-        <v>6660755</v>
+        <v>6660481</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2939,12 +2939,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2975,10 +2975,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121354256</v>
+        <v>121354239</v>
       </c>
       <c r="B22" t="n">
-        <v>100269</v>
+        <v>100270</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696843</v>
+        <v>696830</v>
       </c>
       <c r="R22" t="n">
-        <v>6660663</v>
+        <v>6660785</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3090,10 +3090,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121354218</v>
+        <v>121354208</v>
       </c>
       <c r="B23" t="n">
-        <v>100269</v>
+        <v>100270</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696810</v>
+        <v>696843</v>
       </c>
       <c r="R23" t="n">
-        <v>6660842</v>
+        <v>6660799</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3169,12 +3169,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3205,10 +3205,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121354241</v>
+        <v>121354228</v>
       </c>
       <c r="B24" t="n">
-        <v>100269</v>
+        <v>91643</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3221,21 +3221,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696825</v>
+        <v>696786</v>
       </c>
       <c r="R24" t="n">
-        <v>6660796</v>
+        <v>6660910</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3320,10 +3320,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121354202</v>
+        <v>121354210</v>
       </c>
       <c r="B25" t="n">
-        <v>100269</v>
+        <v>98073</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3336,21 +3336,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696939</v>
+        <v>696874</v>
       </c>
       <c r="R25" t="n">
-        <v>6660882</v>
+        <v>6660666</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3435,10 +3435,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121354156</v>
+        <v>121354165</v>
       </c>
       <c r="B26" t="n">
-        <v>100360</v>
+        <v>100361</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696718</v>
+        <v>696683</v>
       </c>
       <c r="R26" t="n">
-        <v>6660612</v>
+        <v>6660536</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3550,10 +3550,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121354165</v>
+        <v>121354245</v>
       </c>
       <c r="B27" t="n">
-        <v>100360</v>
+        <v>100270</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3566,21 +3566,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696683</v>
+        <v>696963</v>
       </c>
       <c r="R27" t="n">
-        <v>6660536</v>
+        <v>6660755</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3629,12 +3629,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3665,10 +3665,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121354237</v>
+        <v>121354202</v>
       </c>
       <c r="B28" t="n">
-        <v>100269</v>
+        <v>100270</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696816</v>
+        <v>696939</v>
       </c>
       <c r="R28" t="n">
-        <v>6660789</v>
+        <v>6660882</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3744,12 +3744,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3780,10 +3780,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121354152</v>
+        <v>121354213</v>
       </c>
       <c r="B29" t="n">
-        <v>91642</v>
+        <v>100270</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3796,21 +3796,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696860</v>
+        <v>696829</v>
       </c>
       <c r="R29" t="n">
-        <v>6660584</v>
+        <v>6660866</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3859,12 +3859,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3895,10 +3895,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121354206</v>
+        <v>121354199</v>
       </c>
       <c r="B30" t="n">
-        <v>98072</v>
+        <v>100270</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3911,21 +3911,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3944,10 +3944,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696910</v>
+        <v>696837</v>
       </c>
       <c r="R30" t="n">
-        <v>6660863</v>
+        <v>6660782</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4010,10 +4010,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121354210</v>
+        <v>121354258</v>
       </c>
       <c r="B31" t="n">
-        <v>98072</v>
+        <v>103609</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4026,21 +4026,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219798</v>
+        <v>222412</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>696874</v>
+        <v>696953</v>
       </c>
       <c r="R31" t="n">
-        <v>6660666</v>
+        <v>6660737</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4089,12 +4089,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4125,10 +4125,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121354230</v>
+        <v>121354247</v>
       </c>
       <c r="B32" t="n">
-        <v>98072</v>
+        <v>100270</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4141,21 +4141,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696816</v>
+        <v>696845</v>
       </c>
       <c r="R32" t="n">
-        <v>6660877</v>
+        <v>6660742</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4240,10 +4240,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121354249</v>
+        <v>121354226</v>
       </c>
       <c r="B33" t="n">
-        <v>100269</v>
+        <v>98073</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4256,21 +4256,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4289,10 +4289,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696815</v>
+        <v>696779</v>
       </c>
       <c r="R33" t="n">
-        <v>6660731</v>
+        <v>6660917</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4355,10 +4355,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121354254</v>
+        <v>121354249</v>
       </c>
       <c r="B34" t="n">
-        <v>100269</v>
+        <v>100270</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>696815</v>
       </c>
       <c r="R34" t="n">
-        <v>6660713</v>
+        <v>6660731</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4470,10 +4470,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121354143</v>
+        <v>121354241</v>
       </c>
       <c r="B35" t="n">
-        <v>100360</v>
+        <v>100270</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4486,21 +4486,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4519,10 +4519,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696882</v>
+        <v>696825</v>
       </c>
       <c r="R35" t="n">
-        <v>6660480</v>
+        <v>6660796</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4549,12 +4549,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 48490-2022 artfynd.xlsx
+++ b/artfynd/A 48490-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121354218</v>
+        <v>121354249</v>
       </c>
       <c r="B2" t="n">
-        <v>100270</v>
+        <v>100273</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>696810</v>
+        <v>696815</v>
       </c>
       <c r="R2" t="n">
-        <v>6660842</v>
+        <v>6660731</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121354234</v>
+        <v>121354202</v>
       </c>
       <c r="B3" t="n">
-        <v>100270</v>
+        <v>100273</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>696786</v>
+        <v>696939</v>
       </c>
       <c r="R3" t="n">
-        <v>6660804</v>
+        <v>6660882</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121354141</v>
+        <v>121354143</v>
       </c>
       <c r="B4" t="n">
-        <v>101264</v>
+        <v>100364</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,21 +921,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>696745</v>
+        <v>696882</v>
       </c>
       <c r="R4" t="n">
-        <v>6660466</v>
+        <v>6660480</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121354206</v>
+        <v>121354228</v>
       </c>
       <c r="B5" t="n">
-        <v>98073</v>
+        <v>91646</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696910</v>
+        <v>696786</v>
       </c>
       <c r="R5" t="n">
-        <v>6660863</v>
+        <v>6660910</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121354237</v>
+        <v>121354265</v>
       </c>
       <c r="B6" t="n">
-        <v>100270</v>
+        <v>100273</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696816</v>
+        <v>696849</v>
       </c>
       <c r="R6" t="n">
-        <v>6660789</v>
+        <v>6660766</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121354154</v>
+        <v>121354237</v>
       </c>
       <c r="B7" t="n">
-        <v>100361</v>
+        <v>100273</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696874</v>
+        <v>696816</v>
       </c>
       <c r="R7" t="n">
-        <v>6660583</v>
+        <v>6660789</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121354223</v>
+        <v>121354216</v>
       </c>
       <c r="B8" t="n">
-        <v>100270</v>
+        <v>91646</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696708</v>
+        <v>696818</v>
       </c>
       <c r="R8" t="n">
-        <v>6660830</v>
+        <v>6660846</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121354256</v>
+        <v>121354230</v>
       </c>
       <c r="B9" t="n">
-        <v>100270</v>
+        <v>98076</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,21 +1496,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696843</v>
+        <v>696816</v>
       </c>
       <c r="R9" t="n">
-        <v>6660663</v>
+        <v>6660877</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121354230</v>
+        <v>121354204</v>
       </c>
       <c r="B10" t="n">
-        <v>98073</v>
+        <v>98076</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696816</v>
+        <v>696959</v>
       </c>
       <c r="R10" t="n">
-        <v>6660877</v>
+        <v>6660847</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,12 +1674,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121354158</v>
+        <v>121354258</v>
       </c>
       <c r="B11" t="n">
-        <v>98073</v>
+        <v>103612</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1726,21 +1726,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>222412</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>696777</v>
+        <v>696953</v>
       </c>
       <c r="R11" t="n">
-        <v>6660623</v>
+        <v>6660737</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121354251</v>
+        <v>121354223</v>
       </c>
       <c r="B12" t="n">
-        <v>90140</v>
+        <v>100273</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,21 +1841,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4191</v>
+        <v>222771</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Geastrum michelianum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Berk. &amp; Broome</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696840</v>
+        <v>696708</v>
       </c>
       <c r="R12" t="n">
-        <v>6660674</v>
+        <v>6660830</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121354156</v>
+        <v>121354158</v>
       </c>
       <c r="B13" t="n">
-        <v>100361</v>
+        <v>98076</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696718</v>
+        <v>696777</v>
       </c>
       <c r="R13" t="n">
-        <v>6660612</v>
+        <v>6660623</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2055,10 +2055,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121354265</v>
+        <v>121354148</v>
       </c>
       <c r="B14" t="n">
-        <v>100270</v>
+        <v>101267</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,21 +2071,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696849</v>
+        <v>696853</v>
       </c>
       <c r="R14" t="n">
-        <v>6660766</v>
+        <v>6660481</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,10 +2170,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121354267</v>
+        <v>121354218</v>
       </c>
       <c r="B15" t="n">
-        <v>100270</v>
+        <v>100273</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696878</v>
+        <v>696810</v>
       </c>
       <c r="R15" t="n">
-        <v>6660770</v>
+        <v>6660842</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121354204</v>
+        <v>121354267</v>
       </c>
       <c r="B16" t="n">
-        <v>98073</v>
+        <v>100273</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,21 +2301,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696959</v>
+        <v>696878</v>
       </c>
       <c r="R16" t="n">
-        <v>6660847</v>
+        <v>6660770</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2400,10 +2400,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121354254</v>
+        <v>121354251</v>
       </c>
       <c r="B17" t="n">
-        <v>100270</v>
+        <v>90143</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2416,21 +2416,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222771</v>
+        <v>4191</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Geastrum michelianum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Berk. &amp; Broome</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696815</v>
+        <v>696840</v>
       </c>
       <c r="R17" t="n">
-        <v>6660713</v>
+        <v>6660674</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2515,10 +2515,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121354143</v>
+        <v>121354247</v>
       </c>
       <c r="B18" t="n">
-        <v>100361</v>
+        <v>100273</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2531,21 +2531,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696882</v>
+        <v>696845</v>
       </c>
       <c r="R18" t="n">
-        <v>6660480</v>
+        <v>6660742</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2594,12 +2594,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2630,10 +2630,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121354152</v>
+        <v>121354208</v>
       </c>
       <c r="B19" t="n">
-        <v>91643</v>
+        <v>100273</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2646,21 +2646,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696860</v>
+        <v>696843</v>
       </c>
       <c r="R19" t="n">
-        <v>6660584</v>
+        <v>6660799</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2745,10 +2745,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121354216</v>
+        <v>121354241</v>
       </c>
       <c r="B20" t="n">
-        <v>91643</v>
+        <v>100273</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2761,21 +2761,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696818</v>
+        <v>696825</v>
       </c>
       <c r="R20" t="n">
-        <v>6660846</v>
+        <v>6660796</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2860,10 +2860,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121354148</v>
+        <v>121354210</v>
       </c>
       <c r="B21" t="n">
-        <v>101264</v>
+        <v>98076</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221235</v>
+        <v>219798</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696853</v>
+        <v>696874</v>
       </c>
       <c r="R21" t="n">
-        <v>6660481</v>
+        <v>6660666</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2975,10 +2975,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121354239</v>
+        <v>121354165</v>
       </c>
       <c r="B22" t="n">
-        <v>100270</v>
+        <v>100364</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2991,21 +2991,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696830</v>
+        <v>696683</v>
       </c>
       <c r="R22" t="n">
-        <v>6660785</v>
+        <v>6660536</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3054,12 +3054,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3090,10 +3090,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121354208</v>
+        <v>121354152</v>
       </c>
       <c r="B23" t="n">
-        <v>100270</v>
+        <v>91646</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3106,21 +3106,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696843</v>
+        <v>696860</v>
       </c>
       <c r="R23" t="n">
-        <v>6660799</v>
+        <v>6660584</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3205,10 +3205,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121354228</v>
+        <v>121354245</v>
       </c>
       <c r="B24" t="n">
-        <v>91643</v>
+        <v>100273</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3221,21 +3221,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696786</v>
+        <v>696963</v>
       </c>
       <c r="R24" t="n">
-        <v>6660910</v>
+        <v>6660755</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3320,10 +3320,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121354210</v>
+        <v>121354254</v>
       </c>
       <c r="B25" t="n">
-        <v>98073</v>
+        <v>100273</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3336,21 +3336,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696874</v>
+        <v>696815</v>
       </c>
       <c r="R25" t="n">
-        <v>6660666</v>
+        <v>6660713</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3399,12 +3399,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3435,10 +3435,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121354165</v>
+        <v>121354256</v>
       </c>
       <c r="B26" t="n">
-        <v>100361</v>
+        <v>100273</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3451,21 +3451,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696683</v>
+        <v>696843</v>
       </c>
       <c r="R26" t="n">
-        <v>6660536</v>
+        <v>6660663</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3514,12 +3514,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3550,10 +3550,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121354245</v>
+        <v>121354206</v>
       </c>
       <c r="B27" t="n">
-        <v>100270</v>
+        <v>98076</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3566,21 +3566,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696963</v>
+        <v>696910</v>
       </c>
       <c r="R27" t="n">
-        <v>6660755</v>
+        <v>6660863</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3629,12 +3629,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3665,10 +3665,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121354202</v>
+        <v>121354239</v>
       </c>
       <c r="B28" t="n">
-        <v>100270</v>
+        <v>100273</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696939</v>
+        <v>696830</v>
       </c>
       <c r="R28" t="n">
-        <v>6660882</v>
+        <v>6660785</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3744,12 +3744,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3780,10 +3780,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121354213</v>
+        <v>121354156</v>
       </c>
       <c r="B29" t="n">
-        <v>100270</v>
+        <v>100364</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3796,21 +3796,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696829</v>
+        <v>696718</v>
       </c>
       <c r="R29" t="n">
-        <v>6660866</v>
+        <v>6660612</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3859,12 +3859,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3895,10 +3895,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121354199</v>
+        <v>121354154</v>
       </c>
       <c r="B30" t="n">
-        <v>100270</v>
+        <v>100364</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3911,21 +3911,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3944,10 +3944,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696837</v>
+        <v>696874</v>
       </c>
       <c r="R30" t="n">
-        <v>6660782</v>
+        <v>6660583</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4010,10 +4010,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121354258</v>
+        <v>121354141</v>
       </c>
       <c r="B31" t="n">
-        <v>103609</v>
+        <v>101267</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4026,21 +4026,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>696953</v>
+        <v>696745</v>
       </c>
       <c r="R31" t="n">
-        <v>6660737</v>
+        <v>6660466</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4089,12 +4089,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4125,10 +4125,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121354247</v>
+        <v>121354234</v>
       </c>
       <c r="B32" t="n">
-        <v>100270</v>
+        <v>100273</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696845</v>
+        <v>696786</v>
       </c>
       <c r="R32" t="n">
-        <v>6660742</v>
+        <v>6660804</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4240,10 +4240,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121354226</v>
+        <v>121354213</v>
       </c>
       <c r="B33" t="n">
-        <v>98073</v>
+        <v>100273</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4256,21 +4256,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4289,10 +4289,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696779</v>
+        <v>696829</v>
       </c>
       <c r="R33" t="n">
-        <v>6660917</v>
+        <v>6660866</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4355,10 +4355,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121354249</v>
+        <v>121354199</v>
       </c>
       <c r="B34" t="n">
-        <v>100270</v>
+        <v>100273</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4404,10 +4404,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696815</v>
+        <v>696837</v>
       </c>
       <c r="R34" t="n">
-        <v>6660731</v>
+        <v>6660782</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4434,12 +4434,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4470,10 +4470,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121354241</v>
+        <v>121354226</v>
       </c>
       <c r="B35" t="n">
-        <v>100270</v>
+        <v>98076</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4486,21 +4486,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4519,10 +4519,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696825</v>
+        <v>696779</v>
       </c>
       <c r="R35" t="n">
-        <v>6660796</v>
+        <v>6660917</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 48490-2022 artfynd.xlsx
+++ b/artfynd/A 48490-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121354249</v>
+        <v>121354226</v>
       </c>
       <c r="B2" t="n">
-        <v>100273</v>
+        <v>98076</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>696815</v>
+        <v>696779</v>
       </c>
       <c r="R2" t="n">
-        <v>6660731</v>
+        <v>6660917</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121354202</v>
+        <v>121354213</v>
       </c>
       <c r="B3" t="n">
         <v>100273</v>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>696939</v>
+        <v>696829</v>
       </c>
       <c r="R3" t="n">
-        <v>6660882</v>
+        <v>6660866</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121354228</v>
+        <v>121354249</v>
       </c>
       <c r="B5" t="n">
-        <v>91646</v>
+        <v>100273</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696786</v>
+        <v>696815</v>
       </c>
       <c r="R5" t="n">
-        <v>6660910</v>
+        <v>6660731</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,7 +1135,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121354265</v>
+        <v>121354199</v>
       </c>
       <c r="B6" t="n">
         <v>100273</v>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696849</v>
+        <v>696837</v>
       </c>
       <c r="R6" t="n">
-        <v>6660766</v>
+        <v>6660782</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121354237</v>
+        <v>121354152</v>
       </c>
       <c r="B7" t="n">
-        <v>100273</v>
+        <v>91646</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696816</v>
+        <v>696860</v>
       </c>
       <c r="R7" t="n">
-        <v>6660789</v>
+        <v>6660584</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121354216</v>
+        <v>121354267</v>
       </c>
       <c r="B8" t="n">
-        <v>91646</v>
+        <v>100273</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696818</v>
+        <v>696878</v>
       </c>
       <c r="R8" t="n">
-        <v>6660846</v>
+        <v>6660770</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121354230</v>
+        <v>121354239</v>
       </c>
       <c r="B9" t="n">
-        <v>98076</v>
+        <v>100273</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,21 +1496,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696816</v>
+        <v>696830</v>
       </c>
       <c r="R9" t="n">
-        <v>6660877</v>
+        <v>6660785</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121354204</v>
+        <v>121354202</v>
       </c>
       <c r="B10" t="n">
-        <v>98076</v>
+        <v>100273</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,21 +1611,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696959</v>
+        <v>696939</v>
       </c>
       <c r="R10" t="n">
-        <v>6660847</v>
+        <v>6660882</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121354258</v>
+        <v>121354204</v>
       </c>
       <c r="B11" t="n">
-        <v>103612</v>
+        <v>98076</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1726,21 +1726,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222412</v>
+        <v>219798</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>696953</v>
+        <v>696959</v>
       </c>
       <c r="R11" t="n">
-        <v>6660737</v>
+        <v>6660847</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,7 +1825,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121354223</v>
+        <v>121354254</v>
       </c>
       <c r="B12" t="n">
         <v>100273</v>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696708</v>
+        <v>696815</v>
       </c>
       <c r="R12" t="n">
-        <v>6660830</v>
+        <v>6660713</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121354158</v>
+        <v>121354154</v>
       </c>
       <c r="B13" t="n">
-        <v>98076</v>
+        <v>100364</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696777</v>
+        <v>696874</v>
       </c>
       <c r="R13" t="n">
-        <v>6660623</v>
+        <v>6660583</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2055,10 +2055,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121354148</v>
+        <v>121354234</v>
       </c>
       <c r="B14" t="n">
-        <v>101267</v>
+        <v>100273</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,21 +2071,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696853</v>
+        <v>696786</v>
       </c>
       <c r="R14" t="n">
-        <v>6660481</v>
+        <v>6660804</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,7 +2170,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121354218</v>
+        <v>121354237</v>
       </c>
       <c r="B15" t="n">
         <v>100273</v>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696810</v>
+        <v>696816</v>
       </c>
       <c r="R15" t="n">
-        <v>6660842</v>
+        <v>6660789</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121354267</v>
+        <v>121354156</v>
       </c>
       <c r="B16" t="n">
-        <v>100273</v>
+        <v>100364</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,21 +2301,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696878</v>
+        <v>696718</v>
       </c>
       <c r="R16" t="n">
-        <v>6660770</v>
+        <v>6660612</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2400,10 +2400,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121354251</v>
+        <v>121354210</v>
       </c>
       <c r="B17" t="n">
-        <v>90143</v>
+        <v>98076</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2416,21 +2416,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4191</v>
+        <v>219798</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Geastrum michelianum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Berk. &amp; Broome</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696840</v>
+        <v>696874</v>
       </c>
       <c r="R17" t="n">
-        <v>6660674</v>
+        <v>6660666</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2479,12 +2479,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2515,7 +2515,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121354247</v>
+        <v>121354223</v>
       </c>
       <c r="B18" t="n">
         <v>100273</v>
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696845</v>
+        <v>696708</v>
       </c>
       <c r="R18" t="n">
-        <v>6660742</v>
+        <v>6660830</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2630,7 +2630,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121354208</v>
+        <v>121354245</v>
       </c>
       <c r="B19" t="n">
         <v>100273</v>
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696843</v>
+        <v>696963</v>
       </c>
       <c r="R19" t="n">
-        <v>6660799</v>
+        <v>6660755</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2709,12 +2709,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2745,7 +2745,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121354241</v>
+        <v>121354247</v>
       </c>
       <c r="B20" t="n">
         <v>100273</v>
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696825</v>
+        <v>696845</v>
       </c>
       <c r="R20" t="n">
-        <v>6660796</v>
+        <v>6660742</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2860,10 +2860,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121354210</v>
+        <v>121354256</v>
       </c>
       <c r="B21" t="n">
-        <v>98076</v>
+        <v>100273</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696874</v>
+        <v>696843</v>
       </c>
       <c r="R21" t="n">
-        <v>6660666</v>
+        <v>6660663</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2939,12 +2939,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2975,10 +2975,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121354165</v>
+        <v>121354141</v>
       </c>
       <c r="B22" t="n">
-        <v>100364</v>
+        <v>101267</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2991,21 +2991,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696683</v>
+        <v>696745</v>
       </c>
       <c r="R22" t="n">
-        <v>6660536</v>
+        <v>6660466</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3090,10 +3090,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121354152</v>
+        <v>121354265</v>
       </c>
       <c r="B23" t="n">
-        <v>91646</v>
+        <v>100273</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3106,21 +3106,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696860</v>
+        <v>696849</v>
       </c>
       <c r="R23" t="n">
-        <v>6660584</v>
+        <v>6660766</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3169,12 +3169,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3205,10 +3205,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121354245</v>
+        <v>121354228</v>
       </c>
       <c r="B24" t="n">
-        <v>100273</v>
+        <v>91646</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3221,21 +3221,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696963</v>
+        <v>696786</v>
       </c>
       <c r="R24" t="n">
-        <v>6660755</v>
+        <v>6660910</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3320,10 +3320,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121354254</v>
+        <v>121354165</v>
       </c>
       <c r="B25" t="n">
-        <v>100273</v>
+        <v>100364</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3336,21 +3336,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696815</v>
+        <v>696683</v>
       </c>
       <c r="R25" t="n">
-        <v>6660713</v>
+        <v>6660536</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3399,12 +3399,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3435,10 +3435,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121354256</v>
+        <v>121354216</v>
       </c>
       <c r="B26" t="n">
-        <v>100273</v>
+        <v>91646</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3451,21 +3451,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696843</v>
+        <v>696818</v>
       </c>
       <c r="R26" t="n">
-        <v>6660663</v>
+        <v>6660846</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3665,10 +3665,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121354239</v>
+        <v>121354258</v>
       </c>
       <c r="B28" t="n">
-        <v>100273</v>
+        <v>103612</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3681,16 +3681,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696830</v>
+        <v>696953</v>
       </c>
       <c r="R28" t="n">
-        <v>6660785</v>
+        <v>6660737</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3780,10 +3780,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121354156</v>
+        <v>121354251</v>
       </c>
       <c r="B29" t="n">
-        <v>100364</v>
+        <v>90143</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3796,21 +3796,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>4191</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum michelianum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Berk. &amp; Broome</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696718</v>
+        <v>696840</v>
       </c>
       <c r="R29" t="n">
-        <v>6660612</v>
+        <v>6660674</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3859,12 +3859,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3895,10 +3895,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121354154</v>
+        <v>121354241</v>
       </c>
       <c r="B30" t="n">
-        <v>100364</v>
+        <v>100273</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3911,21 +3911,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3944,10 +3944,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696874</v>
+        <v>696825</v>
       </c>
       <c r="R30" t="n">
-        <v>6660583</v>
+        <v>6660796</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3974,12 +3974,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4010,10 +4010,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121354141</v>
+        <v>121354158</v>
       </c>
       <c r="B31" t="n">
-        <v>101267</v>
+        <v>98076</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4026,21 +4026,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221235</v>
+        <v>219798</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>696745</v>
+        <v>696777</v>
       </c>
       <c r="R31" t="n">
-        <v>6660466</v>
+        <v>6660623</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4125,10 +4125,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121354234</v>
+        <v>121354230</v>
       </c>
       <c r="B32" t="n">
-        <v>100273</v>
+        <v>98076</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4141,21 +4141,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696786</v>
+        <v>696816</v>
       </c>
       <c r="R32" t="n">
-        <v>6660804</v>
+        <v>6660877</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4240,10 +4240,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121354213</v>
+        <v>121354148</v>
       </c>
       <c r="B33" t="n">
-        <v>100273</v>
+        <v>101267</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4256,21 +4256,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4289,10 +4289,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696829</v>
+        <v>696853</v>
       </c>
       <c r="R33" t="n">
-        <v>6660866</v>
+        <v>6660481</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4319,12 +4319,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4355,7 +4355,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121354199</v>
+        <v>121354218</v>
       </c>
       <c r="B34" t="n">
         <v>100273</v>
@@ -4404,10 +4404,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696837</v>
+        <v>696810</v>
       </c>
       <c r="R34" t="n">
-        <v>6660782</v>
+        <v>6660842</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4434,12 +4434,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4470,10 +4470,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121354226</v>
+        <v>121354208</v>
       </c>
       <c r="B35" t="n">
-        <v>98076</v>
+        <v>100273</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4486,21 +4486,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4519,10 +4519,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696779</v>
+        <v>696843</v>
       </c>
       <c r="R35" t="n">
-        <v>6660917</v>
+        <v>6660799</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4549,12 +4549,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 48490-2022 artfynd.xlsx
+++ b/artfynd/A 48490-2022 artfynd.xlsx
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121354152</v>
+        <v>121354267</v>
       </c>
       <c r="B7" t="n">
-        <v>91646</v>
+        <v>100273</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696860</v>
+        <v>696878</v>
       </c>
       <c r="R7" t="n">
-        <v>6660584</v>
+        <v>6660770</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121354267</v>
+        <v>121354152</v>
       </c>
       <c r="B8" t="n">
-        <v>100273</v>
+        <v>91646</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696878</v>
+        <v>696860</v>
       </c>
       <c r="R8" t="n">
-        <v>6660770</v>
+        <v>6660584</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1940,10 +1940,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121354154</v>
+        <v>121354234</v>
       </c>
       <c r="B13" t="n">
-        <v>100364</v>
+        <v>100273</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696874</v>
+        <v>696786</v>
       </c>
       <c r="R13" t="n">
-        <v>6660583</v>
+        <v>6660804</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,12 +2019,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2055,10 +2055,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121354234</v>
+        <v>121354154</v>
       </c>
       <c r="B14" t="n">
-        <v>100273</v>
+        <v>100364</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,21 +2071,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696786</v>
+        <v>696874</v>
       </c>
       <c r="R14" t="n">
-        <v>6660804</v>
+        <v>6660583</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,10 +2170,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121354237</v>
+        <v>121354156</v>
       </c>
       <c r="B15" t="n">
-        <v>100273</v>
+        <v>100364</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2186,21 +2186,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696816</v>
+        <v>696718</v>
       </c>
       <c r="R15" t="n">
-        <v>6660789</v>
+        <v>6660612</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2249,12 +2249,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121354156</v>
+        <v>121354237</v>
       </c>
       <c r="B16" t="n">
-        <v>100364</v>
+        <v>100273</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,21 +2301,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696718</v>
+        <v>696816</v>
       </c>
       <c r="R16" t="n">
-        <v>6660612</v>
+        <v>6660789</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 48490-2022 artfynd.xlsx
+++ b/artfynd/A 48490-2022 artfynd.xlsx
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121354267</v>
+        <v>121354152</v>
       </c>
       <c r="B7" t="n">
-        <v>100273</v>
+        <v>91646</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696878</v>
+        <v>696860</v>
       </c>
       <c r="R7" t="n">
-        <v>6660770</v>
+        <v>6660584</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121354152</v>
+        <v>121354267</v>
       </c>
       <c r="B8" t="n">
-        <v>91646</v>
+        <v>100273</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696860</v>
+        <v>696878</v>
       </c>
       <c r="R8" t="n">
-        <v>6660584</v>
+        <v>6660770</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1940,10 +1940,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121354234</v>
+        <v>121354154</v>
       </c>
       <c r="B13" t="n">
-        <v>100273</v>
+        <v>100364</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696786</v>
+        <v>696874</v>
       </c>
       <c r="R13" t="n">
-        <v>6660804</v>
+        <v>6660583</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,12 +2019,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2055,10 +2055,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121354154</v>
+        <v>121354234</v>
       </c>
       <c r="B14" t="n">
-        <v>100364</v>
+        <v>100273</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,21 +2071,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696874</v>
+        <v>696786</v>
       </c>
       <c r="R14" t="n">
-        <v>6660583</v>
+        <v>6660804</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,10 +2170,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121354156</v>
+        <v>121354237</v>
       </c>
       <c r="B15" t="n">
-        <v>100364</v>
+        <v>100273</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2186,21 +2186,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696718</v>
+        <v>696816</v>
       </c>
       <c r="R15" t="n">
-        <v>6660612</v>
+        <v>6660789</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2249,12 +2249,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121354237</v>
+        <v>121354156</v>
       </c>
       <c r="B16" t="n">
-        <v>100273</v>
+        <v>100364</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,21 +2301,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696816</v>
+        <v>696718</v>
       </c>
       <c r="R16" t="n">
-        <v>6660789</v>
+        <v>6660612</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3090,10 +3090,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121354265</v>
+        <v>121354228</v>
       </c>
       <c r="B23" t="n">
-        <v>100273</v>
+        <v>91646</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3106,21 +3106,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696849</v>
+        <v>696786</v>
       </c>
       <c r="R23" t="n">
-        <v>6660766</v>
+        <v>6660910</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3205,10 +3205,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121354228</v>
+        <v>121354165</v>
       </c>
       <c r="B24" t="n">
-        <v>91646</v>
+        <v>100364</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3221,21 +3221,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696786</v>
+        <v>696683</v>
       </c>
       <c r="R24" t="n">
-        <v>6660910</v>
+        <v>6660536</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3284,12 +3284,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3320,10 +3320,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121354165</v>
+        <v>121354265</v>
       </c>
       <c r="B25" t="n">
-        <v>100364</v>
+        <v>100273</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3336,21 +3336,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696683</v>
+        <v>696849</v>
       </c>
       <c r="R25" t="n">
-        <v>6660536</v>
+        <v>6660766</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3399,12 +3399,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 48490-2022 artfynd.xlsx
+++ b/artfynd/A 48490-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121354226</v>
+        <v>121354223</v>
       </c>
       <c r="B2" t="n">
-        <v>98076</v>
+        <v>100279</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>696779</v>
+        <v>696708</v>
       </c>
       <c r="R2" t="n">
-        <v>6660917</v>
+        <v>6660830</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121354213</v>
+        <v>121354247</v>
       </c>
       <c r="B3" t="n">
-        <v>100273</v>
+        <v>100279</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>696829</v>
+        <v>696845</v>
       </c>
       <c r="R3" t="n">
-        <v>6660866</v>
+        <v>6660742</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121354143</v>
+        <v>121354204</v>
       </c>
       <c r="B4" t="n">
-        <v>100364</v>
+        <v>98082</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,21 +921,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>696882</v>
+        <v>696959</v>
       </c>
       <c r="R4" t="n">
-        <v>6660480</v>
+        <v>6660847</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121354249</v>
+        <v>121354154</v>
       </c>
       <c r="B5" t="n">
-        <v>100273</v>
+        <v>100370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696815</v>
+        <v>696874</v>
       </c>
       <c r="R5" t="n">
-        <v>6660731</v>
+        <v>6660583</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121354199</v>
+        <v>121354245</v>
       </c>
       <c r="B6" t="n">
-        <v>100273</v>
+        <v>100279</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696837</v>
+        <v>696963</v>
       </c>
       <c r="R6" t="n">
-        <v>6660782</v>
+        <v>6660755</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121354152</v>
+        <v>121354258</v>
       </c>
       <c r="B7" t="n">
-        <v>91646</v>
+        <v>103618</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>222412</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696860</v>
+        <v>696953</v>
       </c>
       <c r="R7" t="n">
-        <v>6660584</v>
+        <v>6660737</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121354267</v>
+        <v>121354251</v>
       </c>
       <c r="B8" t="n">
-        <v>100273</v>
+        <v>90149</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222771</v>
+        <v>4191</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Geastrum michelianum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Berk. &amp; Broome</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696878</v>
+        <v>696840</v>
       </c>
       <c r="R8" t="n">
-        <v>6660770</v>
+        <v>6660674</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121354239</v>
+        <v>121354199</v>
       </c>
       <c r="B9" t="n">
-        <v>100273</v>
+        <v>100279</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696830</v>
+        <v>696837</v>
       </c>
       <c r="R9" t="n">
-        <v>6660785</v>
+        <v>6660782</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121354202</v>
+        <v>121354158</v>
       </c>
       <c r="B10" t="n">
-        <v>100273</v>
+        <v>98082</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,21 +1611,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696939</v>
+        <v>696777</v>
       </c>
       <c r="R10" t="n">
-        <v>6660882</v>
+        <v>6660623</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121354204</v>
+        <v>121354226</v>
       </c>
       <c r="B11" t="n">
-        <v>98076</v>
+        <v>98082</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>696959</v>
+        <v>696779</v>
       </c>
       <c r="R11" t="n">
-        <v>6660847</v>
+        <v>6660917</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121354254</v>
+        <v>121354148</v>
       </c>
       <c r="B12" t="n">
-        <v>100273</v>
+        <v>101273</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,21 +1841,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696815</v>
+        <v>696853</v>
       </c>
       <c r="R12" t="n">
-        <v>6660713</v>
+        <v>6660481</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1904,12 +1904,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,10 +1940,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121354154</v>
+        <v>121354241</v>
       </c>
       <c r="B13" t="n">
-        <v>100364</v>
+        <v>100279</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696874</v>
+        <v>696825</v>
       </c>
       <c r="R13" t="n">
-        <v>6660583</v>
+        <v>6660796</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,12 +2019,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2055,10 +2055,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121354234</v>
+        <v>121354216</v>
       </c>
       <c r="B14" t="n">
-        <v>100273</v>
+        <v>91652</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,21 +2071,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696786</v>
+        <v>696818</v>
       </c>
       <c r="R14" t="n">
-        <v>6660804</v>
+        <v>6660846</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2170,10 +2170,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121354237</v>
+        <v>121354218</v>
       </c>
       <c r="B15" t="n">
-        <v>100273</v>
+        <v>100279</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696816</v>
+        <v>696810</v>
       </c>
       <c r="R15" t="n">
-        <v>6660789</v>
+        <v>6660842</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121354156</v>
+        <v>121354239</v>
       </c>
       <c r="B16" t="n">
-        <v>100364</v>
+        <v>100279</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,21 +2301,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696718</v>
+        <v>696830</v>
       </c>
       <c r="R16" t="n">
-        <v>6660612</v>
+        <v>6660785</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2400,10 +2400,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121354210</v>
+        <v>121354254</v>
       </c>
       <c r="B17" t="n">
-        <v>98076</v>
+        <v>100279</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2416,21 +2416,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696874</v>
+        <v>696815</v>
       </c>
       <c r="R17" t="n">
-        <v>6660666</v>
+        <v>6660713</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2479,12 +2479,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2515,10 +2515,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121354223</v>
+        <v>121354202</v>
       </c>
       <c r="B18" t="n">
-        <v>100273</v>
+        <v>100279</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696708</v>
+        <v>696939</v>
       </c>
       <c r="R18" t="n">
-        <v>6660830</v>
+        <v>6660882</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2594,12 +2594,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2630,10 +2630,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121354245</v>
+        <v>121354208</v>
       </c>
       <c r="B19" t="n">
-        <v>100273</v>
+        <v>100279</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696963</v>
+        <v>696843</v>
       </c>
       <c r="R19" t="n">
-        <v>6660755</v>
+        <v>6660799</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2709,12 +2709,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2745,10 +2745,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121354247</v>
+        <v>121354228</v>
       </c>
       <c r="B20" t="n">
-        <v>100273</v>
+        <v>91652</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2761,21 +2761,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696845</v>
+        <v>696786</v>
       </c>
       <c r="R20" t="n">
-        <v>6660742</v>
+        <v>6660910</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2860,10 +2860,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121354256</v>
+        <v>121354152</v>
       </c>
       <c r="B21" t="n">
-        <v>100273</v>
+        <v>91652</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696843</v>
+        <v>696860</v>
       </c>
       <c r="R21" t="n">
-        <v>6660663</v>
+        <v>6660584</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2939,12 +2939,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2975,10 +2975,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121354141</v>
+        <v>121354165</v>
       </c>
       <c r="B22" t="n">
-        <v>101267</v>
+        <v>100370</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2991,21 +2991,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696745</v>
+        <v>696683</v>
       </c>
       <c r="R22" t="n">
-        <v>6660466</v>
+        <v>6660536</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3090,10 +3090,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121354228</v>
+        <v>121354249</v>
       </c>
       <c r="B23" t="n">
-        <v>91646</v>
+        <v>100279</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3106,21 +3106,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696786</v>
+        <v>696815</v>
       </c>
       <c r="R23" t="n">
-        <v>6660910</v>
+        <v>6660731</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3205,10 +3205,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121354165</v>
+        <v>121354206</v>
       </c>
       <c r="B24" t="n">
-        <v>100364</v>
+        <v>98082</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3221,21 +3221,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696683</v>
+        <v>696910</v>
       </c>
       <c r="R24" t="n">
-        <v>6660536</v>
+        <v>6660863</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3320,10 +3320,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121354265</v>
+        <v>121354143</v>
       </c>
       <c r="B25" t="n">
-        <v>100273</v>
+        <v>100370</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3336,21 +3336,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696849</v>
+        <v>696882</v>
       </c>
       <c r="R25" t="n">
-        <v>6660766</v>
+        <v>6660480</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3399,12 +3399,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3435,10 +3435,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121354216</v>
+        <v>121354141</v>
       </c>
       <c r="B26" t="n">
-        <v>91646</v>
+        <v>101273</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3451,21 +3451,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4769</v>
+        <v>221235</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696818</v>
+        <v>696745</v>
       </c>
       <c r="R26" t="n">
-        <v>6660846</v>
+        <v>6660466</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3514,12 +3514,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3550,10 +3550,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121354206</v>
+        <v>121354256</v>
       </c>
       <c r="B27" t="n">
-        <v>98076</v>
+        <v>100279</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3566,21 +3566,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696910</v>
+        <v>696843</v>
       </c>
       <c r="R27" t="n">
-        <v>6660863</v>
+        <v>6660663</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3629,12 +3629,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3665,10 +3665,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121354258</v>
+        <v>121354267</v>
       </c>
       <c r="B28" t="n">
-        <v>103612</v>
+        <v>100279</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3681,16 +3681,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222412</v>
+        <v>222771</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696953</v>
+        <v>696878</v>
       </c>
       <c r="R28" t="n">
-        <v>6660737</v>
+        <v>6660770</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3780,10 +3780,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121354251</v>
+        <v>121354210</v>
       </c>
       <c r="B29" t="n">
-        <v>90143</v>
+        <v>98082</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3796,21 +3796,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4191</v>
+        <v>219798</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Geastrum michelianum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Berk. &amp; Broome</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696840</v>
+        <v>696874</v>
       </c>
       <c r="R29" t="n">
-        <v>6660674</v>
+        <v>6660666</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3859,12 +3859,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3895,10 +3895,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121354241</v>
+        <v>121354213</v>
       </c>
       <c r="B30" t="n">
-        <v>100273</v>
+        <v>100279</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3944,10 +3944,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696825</v>
+        <v>696829</v>
       </c>
       <c r="R30" t="n">
-        <v>6660796</v>
+        <v>6660866</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4010,10 +4010,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121354158</v>
+        <v>121354237</v>
       </c>
       <c r="B31" t="n">
-        <v>98076</v>
+        <v>100279</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4026,21 +4026,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>696777</v>
+        <v>696816</v>
       </c>
       <c r="R31" t="n">
-        <v>6660623</v>
+        <v>6660789</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4089,12 +4089,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4125,10 +4125,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121354230</v>
+        <v>121354156</v>
       </c>
       <c r="B32" t="n">
-        <v>98076</v>
+        <v>100370</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4141,21 +4141,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696816</v>
+        <v>696718</v>
       </c>
       <c r="R32" t="n">
-        <v>6660877</v>
+        <v>6660612</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4204,12 +4204,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4240,10 +4240,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121354148</v>
+        <v>121354234</v>
       </c>
       <c r="B33" t="n">
-        <v>101267</v>
+        <v>100279</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4256,21 +4256,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4289,10 +4289,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696853</v>
+        <v>696786</v>
       </c>
       <c r="R33" t="n">
-        <v>6660481</v>
+        <v>6660804</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4319,12 +4319,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4355,10 +4355,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121354218</v>
+        <v>121354265</v>
       </c>
       <c r="B34" t="n">
-        <v>100273</v>
+        <v>100279</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4404,10 +4404,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696810</v>
+        <v>696849</v>
       </c>
       <c r="R34" t="n">
-        <v>6660842</v>
+        <v>6660766</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4470,10 +4470,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121354208</v>
+        <v>121354230</v>
       </c>
       <c r="B35" t="n">
-        <v>100273</v>
+        <v>98082</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4486,21 +4486,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4519,10 +4519,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696843</v>
+        <v>696816</v>
       </c>
       <c r="R35" t="n">
-        <v>6660799</v>
+        <v>6660877</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4549,12 +4549,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 48490-2022 artfynd.xlsx
+++ b/artfynd/A 48490-2022 artfynd.xlsx
@@ -2745,10 +2745,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121354228</v>
+        <v>121354249</v>
       </c>
       <c r="B20" t="n">
-        <v>91652</v>
+        <v>100279</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2761,21 +2761,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696786</v>
+        <v>696815</v>
       </c>
       <c r="R20" t="n">
-        <v>6660910</v>
+        <v>6660731</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2860,7 +2860,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121354152</v>
+        <v>121354228</v>
       </c>
       <c r="B21" t="n">
         <v>91652</v>
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696860</v>
+        <v>696786</v>
       </c>
       <c r="R21" t="n">
-        <v>6660584</v>
+        <v>6660910</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2939,12 +2939,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2975,10 +2975,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121354165</v>
+        <v>121354152</v>
       </c>
       <c r="B22" t="n">
-        <v>100370</v>
+        <v>91652</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2991,21 +2991,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696683</v>
+        <v>696860</v>
       </c>
       <c r="R22" t="n">
-        <v>6660536</v>
+        <v>6660584</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3090,10 +3090,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121354249</v>
+        <v>121354165</v>
       </c>
       <c r="B23" t="n">
-        <v>100279</v>
+        <v>100370</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3106,21 +3106,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696815</v>
+        <v>696683</v>
       </c>
       <c r="R23" t="n">
-        <v>6660731</v>
+        <v>6660536</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3169,12 +3169,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 48490-2022 artfynd.xlsx
+++ b/artfynd/A 48490-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121354223</v>
+        <v>121354251</v>
       </c>
       <c r="B2" t="n">
-        <v>100279</v>
+        <v>90150</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>4191</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Geastrum michelianum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Berk. &amp; Broome</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>696708</v>
+        <v>696840</v>
       </c>
       <c r="R2" t="n">
-        <v>6660830</v>
+        <v>6660674</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121354247</v>
+        <v>121354216</v>
       </c>
       <c r="B3" t="n">
-        <v>100279</v>
+        <v>91653</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>696845</v>
+        <v>696818</v>
       </c>
       <c r="R3" t="n">
-        <v>6660742</v>
+        <v>6660846</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121354204</v>
+        <v>121354256</v>
       </c>
       <c r="B4" t="n">
-        <v>98082</v>
+        <v>100280</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,21 +921,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>696959</v>
+        <v>696843</v>
       </c>
       <c r="R4" t="n">
-        <v>6660847</v>
+        <v>6660663</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,12 +984,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121354154</v>
+        <v>121354156</v>
       </c>
       <c r="B5" t="n">
-        <v>100370</v>
+        <v>100371</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696874</v>
+        <v>696718</v>
       </c>
       <c r="R5" t="n">
-        <v>6660583</v>
+        <v>6660612</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121354245</v>
+        <v>121354241</v>
       </c>
       <c r="B6" t="n">
-        <v>100279</v>
+        <v>100280</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696963</v>
+        <v>696825</v>
       </c>
       <c r="R6" t="n">
-        <v>6660755</v>
+        <v>6660796</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121354258</v>
+        <v>121354154</v>
       </c>
       <c r="B7" t="n">
-        <v>103618</v>
+        <v>100371</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696953</v>
+        <v>696874</v>
       </c>
       <c r="R7" t="n">
-        <v>6660737</v>
+        <v>6660583</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121354251</v>
+        <v>121354148</v>
       </c>
       <c r="B8" t="n">
-        <v>90149</v>
+        <v>101274</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4191</v>
+        <v>221235</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Geastrum michelianum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Berk. &amp; Broome</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696840</v>
+        <v>696853</v>
       </c>
       <c r="R8" t="n">
-        <v>6660674</v>
+        <v>6660481</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121354199</v>
+        <v>121354206</v>
       </c>
       <c r="B9" t="n">
-        <v>100279</v>
+        <v>98083</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,21 +1496,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696837</v>
+        <v>696910</v>
       </c>
       <c r="R9" t="n">
-        <v>6660782</v>
+        <v>6660863</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121354158</v>
+        <v>121354239</v>
       </c>
       <c r="B10" t="n">
-        <v>98082</v>
+        <v>100280</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,21 +1611,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696777</v>
+        <v>696830</v>
       </c>
       <c r="R10" t="n">
-        <v>6660623</v>
+        <v>6660785</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,12 +1674,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121354226</v>
+        <v>121354223</v>
       </c>
       <c r="B11" t="n">
-        <v>98082</v>
+        <v>100280</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1726,21 +1726,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>696779</v>
+        <v>696708</v>
       </c>
       <c r="R11" t="n">
-        <v>6660917</v>
+        <v>6660830</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121354148</v>
+        <v>121354265</v>
       </c>
       <c r="B12" t="n">
-        <v>101273</v>
+        <v>100280</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,21 +1841,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696853</v>
+        <v>696849</v>
       </c>
       <c r="R12" t="n">
-        <v>6660481</v>
+        <v>6660766</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1904,12 +1904,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,10 +1940,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121354241</v>
+        <v>121354258</v>
       </c>
       <c r="B13" t="n">
-        <v>100279</v>
+        <v>103619</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,16 +1956,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696825</v>
+        <v>696953</v>
       </c>
       <c r="R13" t="n">
-        <v>6660796</v>
+        <v>6660737</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2055,10 +2055,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121354216</v>
+        <v>121354143</v>
       </c>
       <c r="B14" t="n">
-        <v>91652</v>
+        <v>100371</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,21 +2071,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696818</v>
+        <v>696882</v>
       </c>
       <c r="R14" t="n">
-        <v>6660846</v>
+        <v>6660480</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,10 +2170,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121354218</v>
+        <v>121354165</v>
       </c>
       <c r="B15" t="n">
-        <v>100279</v>
+        <v>100371</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2186,21 +2186,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696810</v>
+        <v>696683</v>
       </c>
       <c r="R15" t="n">
-        <v>6660842</v>
+        <v>6660536</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2249,12 +2249,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121354239</v>
+        <v>121354210</v>
       </c>
       <c r="B16" t="n">
-        <v>100279</v>
+        <v>98083</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,21 +2301,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696830</v>
+        <v>696874</v>
       </c>
       <c r="R16" t="n">
-        <v>6660785</v>
+        <v>6660666</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2400,10 +2400,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121354254</v>
+        <v>121354234</v>
       </c>
       <c r="B17" t="n">
-        <v>100279</v>
+        <v>100280</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696815</v>
+        <v>696786</v>
       </c>
       <c r="R17" t="n">
-        <v>6660713</v>
+        <v>6660804</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2515,10 +2515,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121354202</v>
+        <v>121354141</v>
       </c>
       <c r="B18" t="n">
-        <v>100279</v>
+        <v>101274</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2531,21 +2531,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696939</v>
+        <v>696745</v>
       </c>
       <c r="R18" t="n">
-        <v>6660882</v>
+        <v>6660466</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2630,10 +2630,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121354208</v>
+        <v>121354199</v>
       </c>
       <c r="B19" t="n">
-        <v>100279</v>
+        <v>100280</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696843</v>
+        <v>696837</v>
       </c>
       <c r="R19" t="n">
-        <v>6660799</v>
+        <v>6660782</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2745,10 +2745,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121354249</v>
+        <v>121354237</v>
       </c>
       <c r="B20" t="n">
-        <v>100279</v>
+        <v>100280</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696815</v>
+        <v>696816</v>
       </c>
       <c r="R20" t="n">
-        <v>6660731</v>
+        <v>6660789</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2860,10 +2860,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121354228</v>
+        <v>121354152</v>
       </c>
       <c r="B21" t="n">
-        <v>91652</v>
+        <v>91653</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696786</v>
+        <v>696860</v>
       </c>
       <c r="R21" t="n">
-        <v>6660910</v>
+        <v>6660584</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2939,12 +2939,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2975,10 +2975,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121354152</v>
+        <v>121354208</v>
       </c>
       <c r="B22" t="n">
-        <v>91652</v>
+        <v>100280</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2991,21 +2991,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696860</v>
+        <v>696843</v>
       </c>
       <c r="R22" t="n">
-        <v>6660584</v>
+        <v>6660799</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3090,10 +3090,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121354165</v>
+        <v>121354213</v>
       </c>
       <c r="B23" t="n">
-        <v>100370</v>
+        <v>100280</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3106,21 +3106,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696683</v>
+        <v>696829</v>
       </c>
       <c r="R23" t="n">
-        <v>6660536</v>
+        <v>6660866</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3169,12 +3169,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3205,10 +3205,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121354206</v>
+        <v>121354249</v>
       </c>
       <c r="B24" t="n">
-        <v>98082</v>
+        <v>100280</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3221,21 +3221,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696910</v>
+        <v>696815</v>
       </c>
       <c r="R24" t="n">
-        <v>6660863</v>
+        <v>6660731</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3284,12 +3284,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3320,10 +3320,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121354143</v>
+        <v>121354202</v>
       </c>
       <c r="B25" t="n">
-        <v>100370</v>
+        <v>100280</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3336,21 +3336,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696882</v>
+        <v>696939</v>
       </c>
       <c r="R25" t="n">
-        <v>6660480</v>
+        <v>6660882</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3435,10 +3435,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121354141</v>
+        <v>121354230</v>
       </c>
       <c r="B26" t="n">
-        <v>101273</v>
+        <v>98083</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3451,21 +3451,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221235</v>
+        <v>219798</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696745</v>
+        <v>696816</v>
       </c>
       <c r="R26" t="n">
-        <v>6660466</v>
+        <v>6660877</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3514,12 +3514,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3550,10 +3550,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121354256</v>
+        <v>121354247</v>
       </c>
       <c r="B27" t="n">
-        <v>100279</v>
+        <v>100280</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696843</v>
+        <v>696845</v>
       </c>
       <c r="R27" t="n">
-        <v>6660663</v>
+        <v>6660742</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3668,7 +3668,7 @@
         <v>121354267</v>
       </c>
       <c r="B28" t="n">
-        <v>100279</v>
+        <v>100280</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3780,10 +3780,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121354210</v>
+        <v>121354158</v>
       </c>
       <c r="B29" t="n">
-        <v>98082</v>
+        <v>98083</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696874</v>
+        <v>696777</v>
       </c>
       <c r="R29" t="n">
-        <v>6660666</v>
+        <v>6660623</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121354213</v>
+        <v>121354226</v>
       </c>
       <c r="B30" t="n">
-        <v>100279</v>
+        <v>98083</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3911,21 +3911,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3944,10 +3944,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696829</v>
+        <v>696779</v>
       </c>
       <c r="R30" t="n">
-        <v>6660866</v>
+        <v>6660917</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4010,10 +4010,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121354237</v>
+        <v>121354204</v>
       </c>
       <c r="B31" t="n">
-        <v>100279</v>
+        <v>98083</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4026,21 +4026,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>696816</v>
+        <v>696959</v>
       </c>
       <c r="R31" t="n">
-        <v>6660789</v>
+        <v>6660847</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4089,12 +4089,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4125,10 +4125,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121354156</v>
+        <v>121354228</v>
       </c>
       <c r="B32" t="n">
-        <v>100370</v>
+        <v>91653</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4141,21 +4141,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696718</v>
+        <v>696786</v>
       </c>
       <c r="R32" t="n">
-        <v>6660612</v>
+        <v>6660910</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4204,12 +4204,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4240,10 +4240,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121354234</v>
+        <v>121354254</v>
       </c>
       <c r="B33" t="n">
-        <v>100279</v>
+        <v>100280</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4289,10 +4289,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696786</v>
+        <v>696815</v>
       </c>
       <c r="R33" t="n">
-        <v>6660804</v>
+        <v>6660713</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4355,10 +4355,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121354265</v>
+        <v>121354218</v>
       </c>
       <c r="B34" t="n">
-        <v>100279</v>
+        <v>100280</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4404,10 +4404,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696849</v>
+        <v>696810</v>
       </c>
       <c r="R34" t="n">
-        <v>6660766</v>
+        <v>6660842</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4470,10 +4470,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121354230</v>
+        <v>121354245</v>
       </c>
       <c r="B35" t="n">
-        <v>98082</v>
+        <v>100280</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4486,21 +4486,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4519,10 +4519,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696816</v>
+        <v>696963</v>
       </c>
       <c r="R35" t="n">
-        <v>6660877</v>
+        <v>6660755</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 48490-2022 artfynd.xlsx
+++ b/artfynd/A 48490-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121354251</v>
+        <v>121354141</v>
       </c>
       <c r="B2" t="n">
-        <v>90150</v>
+        <v>101274</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4191</v>
+        <v>221235</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Geastrum michelianum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Berk. &amp; Broome</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>696840</v>
+        <v>696745</v>
       </c>
       <c r="R2" t="n">
-        <v>6660674</v>
+        <v>6660466</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121354216</v>
+        <v>121354226</v>
       </c>
       <c r="B3" t="n">
-        <v>91653</v>
+        <v>98083</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>696818</v>
+        <v>696779</v>
       </c>
       <c r="R3" t="n">
-        <v>6660846</v>
+        <v>6660917</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121354256</v>
+        <v>121354148</v>
       </c>
       <c r="B4" t="n">
-        <v>100280</v>
+        <v>101274</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,21 +921,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>696843</v>
+        <v>696853</v>
       </c>
       <c r="R4" t="n">
-        <v>6660663</v>
+        <v>6660481</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,12 +984,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121354156</v>
+        <v>121354265</v>
       </c>
       <c r="B5" t="n">
-        <v>100371</v>
+        <v>100280</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696718</v>
+        <v>696849</v>
       </c>
       <c r="R5" t="n">
-        <v>6660612</v>
+        <v>6660766</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,7 +1135,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121354241</v>
+        <v>121354223</v>
       </c>
       <c r="B6" t="n">
         <v>100280</v>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696825</v>
+        <v>696708</v>
       </c>
       <c r="R6" t="n">
-        <v>6660796</v>
+        <v>6660830</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121354154</v>
+        <v>121354152</v>
       </c>
       <c r="B7" t="n">
-        <v>100371</v>
+        <v>91653</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696874</v>
+        <v>696860</v>
       </c>
       <c r="R7" t="n">
-        <v>6660583</v>
+        <v>6660584</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121354148</v>
+        <v>121354247</v>
       </c>
       <c r="B8" t="n">
-        <v>101274</v>
+        <v>100280</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696853</v>
+        <v>696845</v>
       </c>
       <c r="R8" t="n">
-        <v>6660481</v>
+        <v>6660742</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121354239</v>
+        <v>121354165</v>
       </c>
       <c r="B10" t="n">
-        <v>100280</v>
+        <v>100371</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,21 +1611,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696830</v>
+        <v>696683</v>
       </c>
       <c r="R10" t="n">
-        <v>6660785</v>
+        <v>6660536</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,12 +1674,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,7 +1710,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121354223</v>
+        <v>121354218</v>
       </c>
       <c r="B11" t="n">
         <v>100280</v>
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>696708</v>
+        <v>696810</v>
       </c>
       <c r="R11" t="n">
-        <v>6660830</v>
+        <v>6660842</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121354265</v>
+        <v>121354230</v>
       </c>
       <c r="B12" t="n">
-        <v>100280</v>
+        <v>98083</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,21 +1841,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696849</v>
+        <v>696816</v>
       </c>
       <c r="R12" t="n">
-        <v>6660766</v>
+        <v>6660877</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121354258</v>
+        <v>121354241</v>
       </c>
       <c r="B13" t="n">
-        <v>103619</v>
+        <v>100280</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,16 +1956,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222412</v>
+        <v>222771</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696953</v>
+        <v>696825</v>
       </c>
       <c r="R13" t="n">
-        <v>6660737</v>
+        <v>6660796</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2055,10 +2055,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121354143</v>
+        <v>121354258</v>
       </c>
       <c r="B14" t="n">
-        <v>100371</v>
+        <v>103619</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,21 +2071,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696882</v>
+        <v>696953</v>
       </c>
       <c r="R14" t="n">
-        <v>6660480</v>
+        <v>6660737</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,7 +2170,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121354165</v>
+        <v>121354156</v>
       </c>
       <c r="B15" t="n">
         <v>100371</v>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696683</v>
+        <v>696718</v>
       </c>
       <c r="R15" t="n">
-        <v>6660536</v>
+        <v>6660612</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121354210</v>
+        <v>121354208</v>
       </c>
       <c r="B16" t="n">
-        <v>98083</v>
+        <v>100280</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,21 +2301,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696874</v>
+        <v>696843</v>
       </c>
       <c r="R16" t="n">
-        <v>6660666</v>
+        <v>6660799</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2400,7 +2400,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121354234</v>
+        <v>121354256</v>
       </c>
       <c r="B17" t="n">
         <v>100280</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696786</v>
+        <v>696843</v>
       </c>
       <c r="R17" t="n">
-        <v>6660804</v>
+        <v>6660663</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2515,10 +2515,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121354141</v>
+        <v>121354249</v>
       </c>
       <c r="B18" t="n">
-        <v>101274</v>
+        <v>100280</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2531,21 +2531,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696745</v>
+        <v>696815</v>
       </c>
       <c r="R18" t="n">
-        <v>6660466</v>
+        <v>6660731</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2594,12 +2594,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2630,7 +2630,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121354199</v>
+        <v>121354234</v>
       </c>
       <c r="B19" t="n">
         <v>100280</v>
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696837</v>
+        <v>696786</v>
       </c>
       <c r="R19" t="n">
-        <v>6660782</v>
+        <v>6660804</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2709,12 +2709,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2745,10 +2745,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121354237</v>
+        <v>121354154</v>
       </c>
       <c r="B20" t="n">
-        <v>100280</v>
+        <v>100371</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2761,21 +2761,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696816</v>
+        <v>696874</v>
       </c>
       <c r="R20" t="n">
-        <v>6660789</v>
+        <v>6660583</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2824,12 +2824,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2860,7 +2860,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121354152</v>
+        <v>121354228</v>
       </c>
       <c r="B21" t="n">
         <v>91653</v>
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696860</v>
+        <v>696786</v>
       </c>
       <c r="R21" t="n">
-        <v>6660584</v>
+        <v>6660910</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2939,12 +2939,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2975,10 +2975,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121354208</v>
+        <v>121354251</v>
       </c>
       <c r="B22" t="n">
-        <v>100280</v>
+        <v>90150</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2991,21 +2991,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222771</v>
+        <v>4191</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Geastrum michelianum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Berk. &amp; Broome</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696843</v>
+        <v>696840</v>
       </c>
       <c r="R22" t="n">
-        <v>6660799</v>
+        <v>6660674</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3054,12 +3054,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3090,10 +3090,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121354213</v>
+        <v>121354143</v>
       </c>
       <c r="B23" t="n">
-        <v>100280</v>
+        <v>100371</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3106,21 +3106,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696829</v>
+        <v>696882</v>
       </c>
       <c r="R23" t="n">
-        <v>6660866</v>
+        <v>6660480</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3169,12 +3169,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3205,7 +3205,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121354249</v>
+        <v>121354199</v>
       </c>
       <c r="B24" t="n">
         <v>100280</v>
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696815</v>
+        <v>696837</v>
       </c>
       <c r="R24" t="n">
-        <v>6660731</v>
+        <v>6660782</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3284,12 +3284,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3320,7 +3320,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121354202</v>
+        <v>121354213</v>
       </c>
       <c r="B25" t="n">
         <v>100280</v>
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696939</v>
+        <v>696829</v>
       </c>
       <c r="R25" t="n">
-        <v>6660882</v>
+        <v>6660866</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3399,12 +3399,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3435,10 +3435,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121354230</v>
+        <v>121354202</v>
       </c>
       <c r="B26" t="n">
-        <v>98083</v>
+        <v>100280</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3451,21 +3451,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696816</v>
+        <v>696939</v>
       </c>
       <c r="R26" t="n">
-        <v>6660877</v>
+        <v>6660882</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3514,12 +3514,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3550,10 +3550,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121354247</v>
+        <v>121354204</v>
       </c>
       <c r="B27" t="n">
-        <v>100280</v>
+        <v>98083</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3566,21 +3566,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696845</v>
+        <v>696959</v>
       </c>
       <c r="R27" t="n">
-        <v>6660742</v>
+        <v>6660847</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3629,12 +3629,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3665,7 +3665,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121354267</v>
+        <v>121354239</v>
       </c>
       <c r="B28" t="n">
         <v>100280</v>
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696878</v>
+        <v>696830</v>
       </c>
       <c r="R28" t="n">
-        <v>6660770</v>
+        <v>6660785</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3780,7 +3780,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121354158</v>
+        <v>121354210</v>
       </c>
       <c r="B29" t="n">
         <v>98083</v>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696777</v>
+        <v>696874</v>
       </c>
       <c r="R29" t="n">
-        <v>6660623</v>
+        <v>6660666</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121354226</v>
+        <v>121354216</v>
       </c>
       <c r="B30" t="n">
-        <v>98083</v>
+        <v>91653</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3911,21 +3911,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3944,10 +3944,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696779</v>
+        <v>696818</v>
       </c>
       <c r="R30" t="n">
-        <v>6660917</v>
+        <v>6660846</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4010,10 +4010,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121354204</v>
+        <v>121354245</v>
       </c>
       <c r="B31" t="n">
-        <v>98083</v>
+        <v>100280</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4026,21 +4026,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>696959</v>
+        <v>696963</v>
       </c>
       <c r="R31" t="n">
-        <v>6660847</v>
+        <v>6660755</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4089,12 +4089,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4125,10 +4125,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121354228</v>
+        <v>121354267</v>
       </c>
       <c r="B32" t="n">
-        <v>91653</v>
+        <v>100280</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4141,21 +4141,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696786</v>
+        <v>696878</v>
       </c>
       <c r="R32" t="n">
-        <v>6660910</v>
+        <v>6660770</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4240,7 +4240,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121354254</v>
+        <v>121354237</v>
       </c>
       <c r="B33" t="n">
         <v>100280</v>
@@ -4289,10 +4289,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696815</v>
+        <v>696816</v>
       </c>
       <c r="R33" t="n">
-        <v>6660713</v>
+        <v>6660789</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4355,10 +4355,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121354218</v>
+        <v>121354158</v>
       </c>
       <c r="B34" t="n">
-        <v>100280</v>
+        <v>98083</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4371,21 +4371,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4404,10 +4404,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696810</v>
+        <v>696777</v>
       </c>
       <c r="R34" t="n">
-        <v>6660842</v>
+        <v>6660623</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4434,12 +4434,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4470,7 +4470,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121354245</v>
+        <v>121354254</v>
       </c>
       <c r="B35" t="n">
         <v>100280</v>
@@ -4519,10 +4519,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696963</v>
+        <v>696815</v>
       </c>
       <c r="R35" t="n">
-        <v>6660755</v>
+        <v>6660713</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 48490-2022 artfynd.xlsx
+++ b/artfynd/A 48490-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121354141</v>
+        <v>121354213</v>
       </c>
       <c r="B2" t="n">
-        <v>101274</v>
+        <v>100280</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>696745</v>
+        <v>696829</v>
       </c>
       <c r="R2" t="n">
-        <v>6660466</v>
+        <v>6660866</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121354226</v>
+        <v>121354245</v>
       </c>
       <c r="B3" t="n">
-        <v>98083</v>
+        <v>100280</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>696779</v>
+        <v>696963</v>
       </c>
       <c r="R3" t="n">
-        <v>6660917</v>
+        <v>6660755</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121354148</v>
+        <v>121354254</v>
       </c>
       <c r="B4" t="n">
-        <v>101274</v>
+        <v>100280</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,21 +921,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>696853</v>
+        <v>696815</v>
       </c>
       <c r="R4" t="n">
-        <v>6660481</v>
+        <v>6660713</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,12 +984,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121354265</v>
+        <v>121354251</v>
       </c>
       <c r="B5" t="n">
-        <v>100280</v>
+        <v>90150</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222771</v>
+        <v>4191</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Geastrum michelianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Berk. &amp; Broome</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696849</v>
+        <v>696840</v>
       </c>
       <c r="R5" t="n">
-        <v>6660766</v>
+        <v>6660674</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,7 +1135,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121354223</v>
+        <v>121354208</v>
       </c>
       <c r="B6" t="n">
         <v>100280</v>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696708</v>
+        <v>696843</v>
       </c>
       <c r="R6" t="n">
-        <v>6660830</v>
+        <v>6660799</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121354152</v>
+        <v>121354199</v>
       </c>
       <c r="B7" t="n">
-        <v>91653</v>
+        <v>100280</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696860</v>
+        <v>696837</v>
       </c>
       <c r="R7" t="n">
-        <v>6660584</v>
+        <v>6660782</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121354247</v>
+        <v>121354141</v>
       </c>
       <c r="B8" t="n">
-        <v>100280</v>
+        <v>101274</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696845</v>
+        <v>696745</v>
       </c>
       <c r="R8" t="n">
-        <v>6660742</v>
+        <v>6660466</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121354206</v>
+        <v>121354216</v>
       </c>
       <c r="B9" t="n">
-        <v>98083</v>
+        <v>91653</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,21 +1496,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696910</v>
+        <v>696818</v>
       </c>
       <c r="R9" t="n">
-        <v>6660863</v>
+        <v>6660846</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121354165</v>
+        <v>121354230</v>
       </c>
       <c r="B10" t="n">
-        <v>100371</v>
+        <v>98083</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,21 +1611,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696683</v>
+        <v>696816</v>
       </c>
       <c r="R10" t="n">
-        <v>6660536</v>
+        <v>6660877</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,12 +1674,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,7 +1710,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121354218</v>
+        <v>121354256</v>
       </c>
       <c r="B11" t="n">
         <v>100280</v>
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>696810</v>
+        <v>696843</v>
       </c>
       <c r="R11" t="n">
-        <v>6660842</v>
+        <v>6660663</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121354230</v>
+        <v>121354267</v>
       </c>
       <c r="B12" t="n">
-        <v>98083</v>
+        <v>100280</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,21 +1841,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696816</v>
+        <v>696878</v>
       </c>
       <c r="R12" t="n">
-        <v>6660877</v>
+        <v>6660770</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,7 +1940,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121354241</v>
+        <v>121354265</v>
       </c>
       <c r="B13" t="n">
         <v>100280</v>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696825</v>
+        <v>696849</v>
       </c>
       <c r="R13" t="n">
-        <v>6660796</v>
+        <v>6660766</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2055,10 +2055,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121354258</v>
+        <v>121354143</v>
       </c>
       <c r="B14" t="n">
-        <v>103619</v>
+        <v>100371</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,21 +2071,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696953</v>
+        <v>696882</v>
       </c>
       <c r="R14" t="n">
-        <v>6660737</v>
+        <v>6660480</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,10 +2170,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121354156</v>
+        <v>121354239</v>
       </c>
       <c r="B15" t="n">
-        <v>100371</v>
+        <v>100280</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2186,21 +2186,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696718</v>
+        <v>696830</v>
       </c>
       <c r="R15" t="n">
-        <v>6660612</v>
+        <v>6660785</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2249,12 +2249,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121354208</v>
+        <v>121354165</v>
       </c>
       <c r="B16" t="n">
-        <v>100280</v>
+        <v>100371</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,21 +2301,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696843</v>
+        <v>696683</v>
       </c>
       <c r="R16" t="n">
-        <v>6660799</v>
+        <v>6660536</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2400,7 +2400,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121354256</v>
+        <v>121354247</v>
       </c>
       <c r="B17" t="n">
         <v>100280</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696843</v>
+        <v>696845</v>
       </c>
       <c r="R17" t="n">
-        <v>6660663</v>
+        <v>6660742</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2515,10 +2515,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121354249</v>
+        <v>121354204</v>
       </c>
       <c r="B18" t="n">
-        <v>100280</v>
+        <v>98083</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2531,21 +2531,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696815</v>
+        <v>696959</v>
       </c>
       <c r="R18" t="n">
-        <v>6660731</v>
+        <v>6660847</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2594,12 +2594,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2630,10 +2630,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121354234</v>
+        <v>121354206</v>
       </c>
       <c r="B19" t="n">
-        <v>100280</v>
+        <v>98083</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2646,21 +2646,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696786</v>
+        <v>696910</v>
       </c>
       <c r="R19" t="n">
-        <v>6660804</v>
+        <v>6660863</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2709,12 +2709,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2745,10 +2745,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121354154</v>
+        <v>121354218</v>
       </c>
       <c r="B20" t="n">
-        <v>100371</v>
+        <v>100280</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2761,21 +2761,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696874</v>
+        <v>696810</v>
       </c>
       <c r="R20" t="n">
-        <v>6660583</v>
+        <v>6660842</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2824,12 +2824,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2860,10 +2860,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121354228</v>
+        <v>121354241</v>
       </c>
       <c r="B21" t="n">
-        <v>91653</v>
+        <v>100280</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696786</v>
+        <v>696825</v>
       </c>
       <c r="R21" t="n">
-        <v>6660910</v>
+        <v>6660796</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2975,10 +2975,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121354251</v>
+        <v>121354202</v>
       </c>
       <c r="B22" t="n">
-        <v>90150</v>
+        <v>100280</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2991,21 +2991,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4191</v>
+        <v>222771</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Geastrum michelianum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Berk. &amp; Broome</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696840</v>
+        <v>696939</v>
       </c>
       <c r="R22" t="n">
-        <v>6660674</v>
+        <v>6660882</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3054,12 +3054,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3090,10 +3090,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121354143</v>
+        <v>121354258</v>
       </c>
       <c r="B23" t="n">
-        <v>100371</v>
+        <v>103619</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3106,21 +3106,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696882</v>
+        <v>696953</v>
       </c>
       <c r="R23" t="n">
-        <v>6660480</v>
+        <v>6660737</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3169,12 +3169,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3205,10 +3205,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121354199</v>
+        <v>121354228</v>
       </c>
       <c r="B24" t="n">
-        <v>100280</v>
+        <v>91653</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3221,21 +3221,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696837</v>
+        <v>696786</v>
       </c>
       <c r="R24" t="n">
-        <v>6660782</v>
+        <v>6660910</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3284,12 +3284,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3320,10 +3320,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121354213</v>
+        <v>121354226</v>
       </c>
       <c r="B25" t="n">
-        <v>100280</v>
+        <v>98083</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3336,21 +3336,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696829</v>
+        <v>696779</v>
       </c>
       <c r="R25" t="n">
-        <v>6660866</v>
+        <v>6660917</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3435,7 +3435,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121354202</v>
+        <v>121354249</v>
       </c>
       <c r="B26" t="n">
         <v>100280</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696939</v>
+        <v>696815</v>
       </c>
       <c r="R26" t="n">
-        <v>6660882</v>
+        <v>6660731</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3514,12 +3514,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3550,10 +3550,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121354204</v>
+        <v>121354152</v>
       </c>
       <c r="B27" t="n">
-        <v>98083</v>
+        <v>91653</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3566,21 +3566,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696959</v>
+        <v>696860</v>
       </c>
       <c r="R27" t="n">
-        <v>6660847</v>
+        <v>6660584</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3665,10 +3665,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121354239</v>
+        <v>121354154</v>
       </c>
       <c r="B28" t="n">
-        <v>100280</v>
+        <v>100371</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3681,21 +3681,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696830</v>
+        <v>696874</v>
       </c>
       <c r="R28" t="n">
-        <v>6660785</v>
+        <v>6660583</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3744,12 +3744,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3780,10 +3780,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121354210</v>
+        <v>121354237</v>
       </c>
       <c r="B29" t="n">
-        <v>98083</v>
+        <v>100280</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3796,21 +3796,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696874</v>
+        <v>696816</v>
       </c>
       <c r="R29" t="n">
-        <v>6660666</v>
+        <v>6660789</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3859,12 +3859,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3895,10 +3895,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121354216</v>
+        <v>121354210</v>
       </c>
       <c r="B30" t="n">
-        <v>91653</v>
+        <v>98083</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3911,21 +3911,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3944,10 +3944,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696818</v>
+        <v>696874</v>
       </c>
       <c r="R30" t="n">
-        <v>6660846</v>
+        <v>6660666</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3974,12 +3974,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4010,10 +4010,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121354245</v>
+        <v>121354158</v>
       </c>
       <c r="B31" t="n">
-        <v>100280</v>
+        <v>98083</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4026,21 +4026,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>696963</v>
+        <v>696777</v>
       </c>
       <c r="R31" t="n">
-        <v>6660755</v>
+        <v>6660623</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4089,12 +4089,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4125,10 +4125,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121354267</v>
+        <v>121354148</v>
       </c>
       <c r="B32" t="n">
-        <v>100280</v>
+        <v>101274</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4141,21 +4141,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696878</v>
+        <v>696853</v>
       </c>
       <c r="R32" t="n">
-        <v>6660770</v>
+        <v>6660481</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4204,12 +4204,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4240,10 +4240,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121354237</v>
+        <v>121354156</v>
       </c>
       <c r="B33" t="n">
-        <v>100280</v>
+        <v>100371</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4256,21 +4256,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4289,10 +4289,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696816</v>
+        <v>696718</v>
       </c>
       <c r="R33" t="n">
-        <v>6660789</v>
+        <v>6660612</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4319,12 +4319,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4355,10 +4355,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121354158</v>
+        <v>121354223</v>
       </c>
       <c r="B34" t="n">
-        <v>98083</v>
+        <v>100280</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4371,21 +4371,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4404,10 +4404,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696777</v>
+        <v>696708</v>
       </c>
       <c r="R34" t="n">
-        <v>6660623</v>
+        <v>6660830</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4434,12 +4434,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4470,7 +4470,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121354254</v>
+        <v>121354234</v>
       </c>
       <c r="B35" t="n">
         <v>100280</v>
@@ -4519,10 +4519,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696815</v>
+        <v>696786</v>
       </c>
       <c r="R35" t="n">
-        <v>6660713</v>
+        <v>6660804</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 48490-2022 artfynd.xlsx
+++ b/artfynd/A 48490-2022 artfynd.xlsx
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121354245</v>
+        <v>121354218</v>
       </c>
       <c r="B3" t="n">
         <v>100280</v>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>696963</v>
+        <v>696810</v>
       </c>
       <c r="R3" t="n">
-        <v>6660755</v>
+        <v>6660842</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121354254</v>
+        <v>121354230</v>
       </c>
       <c r="B4" t="n">
-        <v>100280</v>
+        <v>98083</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,21 +921,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>696815</v>
+        <v>696816</v>
       </c>
       <c r="R4" t="n">
-        <v>6660713</v>
+        <v>6660877</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121354251</v>
+        <v>121354204</v>
       </c>
       <c r="B5" t="n">
-        <v>90150</v>
+        <v>98083</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4191</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Geastrum michelianum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Berk. &amp; Broome</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696840</v>
+        <v>696959</v>
       </c>
       <c r="R5" t="n">
-        <v>6660674</v>
+        <v>6660847</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121354208</v>
+        <v>121354165</v>
       </c>
       <c r="B6" t="n">
-        <v>100280</v>
+        <v>100371</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,21 +1151,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696843</v>
+        <v>696683</v>
       </c>
       <c r="R6" t="n">
-        <v>6660799</v>
+        <v>6660536</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121354199</v>
+        <v>121354239</v>
       </c>
       <c r="B7" t="n">
         <v>100280</v>
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696837</v>
+        <v>696830</v>
       </c>
       <c r="R7" t="n">
-        <v>6660782</v>
+        <v>6660785</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121354141</v>
+        <v>121354249</v>
       </c>
       <c r="B8" t="n">
-        <v>101274</v>
+        <v>100280</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696745</v>
+        <v>696815</v>
       </c>
       <c r="R8" t="n">
-        <v>6660466</v>
+        <v>6660731</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121354216</v>
+        <v>121354267</v>
       </c>
       <c r="B9" t="n">
-        <v>91653</v>
+        <v>100280</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,21 +1496,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696818</v>
+        <v>696878</v>
       </c>
       <c r="R9" t="n">
-        <v>6660846</v>
+        <v>6660770</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121354230</v>
+        <v>121354254</v>
       </c>
       <c r="B10" t="n">
-        <v>98083</v>
+        <v>100280</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,21 +1611,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696816</v>
+        <v>696815</v>
       </c>
       <c r="R10" t="n">
-        <v>6660877</v>
+        <v>6660713</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121354256</v>
+        <v>121354216</v>
       </c>
       <c r="B11" t="n">
-        <v>100280</v>
+        <v>91653</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1726,21 +1726,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>696843</v>
+        <v>696818</v>
       </c>
       <c r="R11" t="n">
-        <v>6660663</v>
+        <v>6660846</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121354267</v>
+        <v>121354247</v>
       </c>
       <c r="B12" t="n">
         <v>100280</v>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696878</v>
+        <v>696845</v>
       </c>
       <c r="R12" t="n">
-        <v>6660770</v>
+        <v>6660742</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,7 +1940,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121354265</v>
+        <v>121354241</v>
       </c>
       <c r="B13" t="n">
         <v>100280</v>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696849</v>
+        <v>696825</v>
       </c>
       <c r="R13" t="n">
-        <v>6660766</v>
+        <v>6660796</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2055,10 +2055,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121354143</v>
+        <v>121354208</v>
       </c>
       <c r="B14" t="n">
-        <v>100371</v>
+        <v>100280</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,21 +2071,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696882</v>
+        <v>696843</v>
       </c>
       <c r="R14" t="n">
-        <v>6660480</v>
+        <v>6660799</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2170,10 +2170,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121354239</v>
+        <v>121354206</v>
       </c>
       <c r="B15" t="n">
-        <v>100280</v>
+        <v>98083</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2186,21 +2186,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696830</v>
+        <v>696910</v>
       </c>
       <c r="R15" t="n">
-        <v>6660785</v>
+        <v>6660863</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2249,12 +2249,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,7 +2285,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121354165</v>
+        <v>121354156</v>
       </c>
       <c r="B16" t="n">
         <v>100371</v>
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696683</v>
+        <v>696718</v>
       </c>
       <c r="R16" t="n">
-        <v>6660536</v>
+        <v>6660612</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2400,7 +2400,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121354247</v>
+        <v>121354223</v>
       </c>
       <c r="B17" t="n">
         <v>100280</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696845</v>
+        <v>696708</v>
       </c>
       <c r="R17" t="n">
-        <v>6660742</v>
+        <v>6660830</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2515,10 +2515,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121354204</v>
+        <v>121354152</v>
       </c>
       <c r="B18" t="n">
-        <v>98083</v>
+        <v>91653</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2531,21 +2531,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696959</v>
+        <v>696860</v>
       </c>
       <c r="R18" t="n">
-        <v>6660847</v>
+        <v>6660584</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2630,10 +2630,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121354206</v>
+        <v>121354143</v>
       </c>
       <c r="B19" t="n">
-        <v>98083</v>
+        <v>100371</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2646,21 +2646,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696910</v>
+        <v>696882</v>
       </c>
       <c r="R19" t="n">
-        <v>6660863</v>
+        <v>6660480</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2745,7 +2745,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121354218</v>
+        <v>121354256</v>
       </c>
       <c r="B20" t="n">
         <v>100280</v>
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696810</v>
+        <v>696843</v>
       </c>
       <c r="R20" t="n">
-        <v>6660842</v>
+        <v>6660663</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2860,7 +2860,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121354241</v>
+        <v>121354265</v>
       </c>
       <c r="B21" t="n">
         <v>100280</v>
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696825</v>
+        <v>696849</v>
       </c>
       <c r="R21" t="n">
-        <v>6660796</v>
+        <v>6660766</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2975,10 +2975,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121354202</v>
+        <v>121354158</v>
       </c>
       <c r="B22" t="n">
-        <v>100280</v>
+        <v>98083</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2991,21 +2991,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696939</v>
+        <v>696777</v>
       </c>
       <c r="R22" t="n">
-        <v>6660882</v>
+        <v>6660623</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3090,10 +3090,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121354258</v>
+        <v>121354210</v>
       </c>
       <c r="B23" t="n">
-        <v>103619</v>
+        <v>98083</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3106,21 +3106,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222412</v>
+        <v>219798</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696953</v>
+        <v>696874</v>
       </c>
       <c r="R23" t="n">
-        <v>6660737</v>
+        <v>6660666</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3169,12 +3169,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3205,10 +3205,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121354228</v>
+        <v>121354154</v>
       </c>
       <c r="B24" t="n">
-        <v>91653</v>
+        <v>100371</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3221,21 +3221,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696786</v>
+        <v>696874</v>
       </c>
       <c r="R24" t="n">
-        <v>6660910</v>
+        <v>6660583</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3284,12 +3284,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3320,10 +3320,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121354226</v>
+        <v>121354202</v>
       </c>
       <c r="B25" t="n">
-        <v>98083</v>
+        <v>100280</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3336,21 +3336,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696779</v>
+        <v>696939</v>
       </c>
       <c r="R25" t="n">
-        <v>6660917</v>
+        <v>6660882</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3399,12 +3399,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3435,10 +3435,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121354249</v>
+        <v>121354258</v>
       </c>
       <c r="B26" t="n">
-        <v>100280</v>
+        <v>103619</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3451,16 +3451,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696815</v>
+        <v>696953</v>
       </c>
       <c r="R26" t="n">
-        <v>6660731</v>
+        <v>6660737</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3550,10 +3550,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121354152</v>
+        <v>121354251</v>
       </c>
       <c r="B27" t="n">
-        <v>91653</v>
+        <v>90150</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3566,21 +3566,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4769</v>
+        <v>4191</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Geastrum michelianum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Berk. &amp; Broome</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696860</v>
+        <v>696840</v>
       </c>
       <c r="R27" t="n">
-        <v>6660584</v>
+        <v>6660674</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3629,12 +3629,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3665,10 +3665,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121354154</v>
+        <v>121354226</v>
       </c>
       <c r="B28" t="n">
-        <v>100371</v>
+        <v>98083</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3681,21 +3681,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696874</v>
+        <v>696779</v>
       </c>
       <c r="R28" t="n">
-        <v>6660583</v>
+        <v>6660917</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3744,12 +3744,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3780,7 +3780,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121354237</v>
+        <v>121354234</v>
       </c>
       <c r="B29" t="n">
         <v>100280</v>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696816</v>
+        <v>696786</v>
       </c>
       <c r="R29" t="n">
-        <v>6660789</v>
+        <v>6660804</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121354210</v>
+        <v>121354245</v>
       </c>
       <c r="B30" t="n">
-        <v>98083</v>
+        <v>100280</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3911,21 +3911,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3944,10 +3944,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696874</v>
+        <v>696963</v>
       </c>
       <c r="R30" t="n">
-        <v>6660666</v>
+        <v>6660755</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3974,12 +3974,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4010,10 +4010,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121354158</v>
+        <v>121354199</v>
       </c>
       <c r="B31" t="n">
-        <v>98083</v>
+        <v>100280</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4026,21 +4026,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>696777</v>
+        <v>696837</v>
       </c>
       <c r="R31" t="n">
-        <v>6660623</v>
+        <v>6660782</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4125,7 +4125,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121354148</v>
+        <v>121354141</v>
       </c>
       <c r="B32" t="n">
         <v>101274</v>
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696853</v>
+        <v>696745</v>
       </c>
       <c r="R32" t="n">
-        <v>6660481</v>
+        <v>6660466</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4240,10 +4240,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121354156</v>
+        <v>121354228</v>
       </c>
       <c r="B33" t="n">
-        <v>100371</v>
+        <v>91653</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4256,21 +4256,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4289,10 +4289,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696718</v>
+        <v>696786</v>
       </c>
       <c r="R33" t="n">
-        <v>6660612</v>
+        <v>6660910</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4319,12 +4319,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4355,10 +4355,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121354223</v>
+        <v>121354148</v>
       </c>
       <c r="B34" t="n">
-        <v>100280</v>
+        <v>101274</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4371,21 +4371,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4404,10 +4404,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696708</v>
+        <v>696853</v>
       </c>
       <c r="R34" t="n">
-        <v>6660830</v>
+        <v>6660481</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4434,12 +4434,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4470,7 +4470,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121354234</v>
+        <v>121354237</v>
       </c>
       <c r="B35" t="n">
         <v>100280</v>
@@ -4519,10 +4519,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696786</v>
+        <v>696816</v>
       </c>
       <c r="R35" t="n">
-        <v>6660804</v>
+        <v>6660789</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 48490-2022 artfynd.xlsx
+++ b/artfynd/A 48490-2022 artfynd.xlsx
@@ -1940,10 +1940,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121354241</v>
+        <v>121354206</v>
       </c>
       <c r="B13" t="n">
-        <v>100280</v>
+        <v>98083</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696825</v>
+        <v>696910</v>
       </c>
       <c r="R13" t="n">
-        <v>6660796</v>
+        <v>6660863</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,12 +2019,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2055,10 +2055,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121354208</v>
+        <v>121354156</v>
       </c>
       <c r="B14" t="n">
-        <v>100280</v>
+        <v>100371</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,21 +2071,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696843</v>
+        <v>696718</v>
       </c>
       <c r="R14" t="n">
-        <v>6660799</v>
+        <v>6660612</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2170,10 +2170,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121354206</v>
+        <v>121354223</v>
       </c>
       <c r="B15" t="n">
-        <v>98083</v>
+        <v>100280</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2186,21 +2186,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696910</v>
+        <v>696708</v>
       </c>
       <c r="R15" t="n">
-        <v>6660863</v>
+        <v>6660830</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2249,12 +2249,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121354156</v>
+        <v>121354241</v>
       </c>
       <c r="B16" t="n">
-        <v>100371</v>
+        <v>100280</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,21 +2301,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696718</v>
+        <v>696825</v>
       </c>
       <c r="R16" t="n">
-        <v>6660612</v>
+        <v>6660796</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2400,7 +2400,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121354223</v>
+        <v>121354208</v>
       </c>
       <c r="B17" t="n">
         <v>100280</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696708</v>
+        <v>696843</v>
       </c>
       <c r="R17" t="n">
-        <v>6660830</v>
+        <v>6660799</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2479,12 +2479,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2745,7 +2745,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121354256</v>
+        <v>121354265</v>
       </c>
       <c r="B20" t="n">
         <v>100280</v>
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696843</v>
+        <v>696849</v>
       </c>
       <c r="R20" t="n">
-        <v>6660663</v>
+        <v>6660766</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2860,7 +2860,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121354265</v>
+        <v>121354256</v>
       </c>
       <c r="B21" t="n">
         <v>100280</v>
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696849</v>
+        <v>696843</v>
       </c>
       <c r="R21" t="n">
-        <v>6660766</v>
+        <v>6660663</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 48490-2022 artfynd.xlsx
+++ b/artfynd/A 48490-2022 artfynd.xlsx
@@ -2515,10 +2515,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121354152</v>
+        <v>121354143</v>
       </c>
       <c r="B18" t="n">
-        <v>91653</v>
+        <v>100371</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2531,21 +2531,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696860</v>
+        <v>696882</v>
       </c>
       <c r="R18" t="n">
-        <v>6660584</v>
+        <v>6660480</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2630,10 +2630,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121354143</v>
+        <v>121354152</v>
       </c>
       <c r="B19" t="n">
-        <v>100371</v>
+        <v>91653</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2646,21 +2646,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696882</v>
+        <v>696860</v>
       </c>
       <c r="R19" t="n">
-        <v>6660480</v>
+        <v>6660584</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 48490-2022 artfynd.xlsx
+++ b/artfynd/A 48490-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121354213</v>
       </c>
       <c r="B2" t="n">
-        <v>100280</v>
+        <v>100288</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121354218</v>
+        <v>121354237</v>
       </c>
       <c r="B3" t="n">
-        <v>100280</v>
+        <v>100288</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>696810</v>
+        <v>696816</v>
       </c>
       <c r="R3" t="n">
-        <v>6660842</v>
+        <v>6660789</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121354230</v>
+        <v>121354204</v>
       </c>
       <c r="B4" t="n">
-        <v>98083</v>
+        <v>98091</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>696816</v>
+        <v>696959</v>
       </c>
       <c r="R4" t="n">
-        <v>6660877</v>
+        <v>6660847</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,12 +984,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121354204</v>
+        <v>121354199</v>
       </c>
       <c r="B5" t="n">
-        <v>98083</v>
+        <v>100288</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696959</v>
+        <v>696837</v>
       </c>
       <c r="R5" t="n">
-        <v>6660847</v>
+        <v>6660782</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121354165</v>
+        <v>121354256</v>
       </c>
       <c r="B6" t="n">
-        <v>100371</v>
+        <v>100288</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,21 +1151,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696683</v>
+        <v>696843</v>
       </c>
       <c r="R6" t="n">
-        <v>6660536</v>
+        <v>6660663</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121354239</v>
+        <v>121354226</v>
       </c>
       <c r="B7" t="n">
-        <v>100280</v>
+        <v>98091</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696830</v>
+        <v>696779</v>
       </c>
       <c r="R7" t="n">
-        <v>6660785</v>
+        <v>6660917</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121354249</v>
+        <v>121354258</v>
       </c>
       <c r="B8" t="n">
-        <v>100280</v>
+        <v>103627</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696815</v>
+        <v>696953</v>
       </c>
       <c r="R8" t="n">
-        <v>6660731</v>
+        <v>6660737</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121354267</v>
+        <v>121354152</v>
       </c>
       <c r="B9" t="n">
-        <v>100280</v>
+        <v>91661</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,21 +1496,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696878</v>
+        <v>696860</v>
       </c>
       <c r="R9" t="n">
-        <v>6660770</v>
+        <v>6660584</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121354254</v>
+        <v>121354247</v>
       </c>
       <c r="B10" t="n">
-        <v>100280</v>
+        <v>100288</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696815</v>
+        <v>696845</v>
       </c>
       <c r="R10" t="n">
-        <v>6660713</v>
+        <v>6660742</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121354216</v>
+        <v>121354206</v>
       </c>
       <c r="B11" t="n">
-        <v>91653</v>
+        <v>98091</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1726,21 +1726,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>696818</v>
+        <v>696910</v>
       </c>
       <c r="R11" t="n">
-        <v>6660846</v>
+        <v>6660863</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121354247</v>
+        <v>121354230</v>
       </c>
       <c r="B12" t="n">
-        <v>100280</v>
+        <v>98091</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,21 +1841,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696845</v>
+        <v>696816</v>
       </c>
       <c r="R12" t="n">
-        <v>6660742</v>
+        <v>6660877</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121354206</v>
+        <v>121354216</v>
       </c>
       <c r="B13" t="n">
-        <v>98083</v>
+        <v>91661</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696910</v>
+        <v>696818</v>
       </c>
       <c r="R13" t="n">
-        <v>6660863</v>
+        <v>6660846</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,12 +2019,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2055,10 +2055,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121354156</v>
+        <v>121354245</v>
       </c>
       <c r="B14" t="n">
-        <v>100371</v>
+        <v>100288</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,21 +2071,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696718</v>
+        <v>696963</v>
       </c>
       <c r="R14" t="n">
-        <v>6660612</v>
+        <v>6660755</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,10 +2170,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121354223</v>
+        <v>121354267</v>
       </c>
       <c r="B15" t="n">
-        <v>100280</v>
+        <v>100288</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696708</v>
+        <v>696878</v>
       </c>
       <c r="R15" t="n">
-        <v>6660830</v>
+        <v>6660770</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121354241</v>
+        <v>121354208</v>
       </c>
       <c r="B16" t="n">
-        <v>100280</v>
+        <v>100288</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696825</v>
+        <v>696843</v>
       </c>
       <c r="R16" t="n">
-        <v>6660796</v>
+        <v>6660799</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2400,10 +2400,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121354208</v>
+        <v>121354265</v>
       </c>
       <c r="B17" t="n">
-        <v>100280</v>
+        <v>100288</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696843</v>
+        <v>696849</v>
       </c>
       <c r="R17" t="n">
-        <v>6660799</v>
+        <v>6660766</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2479,12 +2479,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2515,10 +2515,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121354143</v>
+        <v>121354148</v>
       </c>
       <c r="B18" t="n">
-        <v>100371</v>
+        <v>101282</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2531,21 +2531,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696882</v>
+        <v>696853</v>
       </c>
       <c r="R18" t="n">
-        <v>6660480</v>
+        <v>6660481</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2630,10 +2630,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121354152</v>
+        <v>121354228</v>
       </c>
       <c r="B19" t="n">
-        <v>91653</v>
+        <v>91661</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696860</v>
+        <v>696786</v>
       </c>
       <c r="R19" t="n">
-        <v>6660584</v>
+        <v>6660910</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2709,12 +2709,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2745,10 +2745,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121354265</v>
+        <v>121354223</v>
       </c>
       <c r="B20" t="n">
-        <v>100280</v>
+        <v>100288</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696849</v>
+        <v>696708</v>
       </c>
       <c r="R20" t="n">
-        <v>6660766</v>
+        <v>6660830</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2860,10 +2860,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121354256</v>
+        <v>121354165</v>
       </c>
       <c r="B21" t="n">
-        <v>100280</v>
+        <v>100379</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696843</v>
+        <v>696683</v>
       </c>
       <c r="R21" t="n">
-        <v>6660663</v>
+        <v>6660536</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2939,12 +2939,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2975,10 +2975,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121354158</v>
+        <v>121354154</v>
       </c>
       <c r="B22" t="n">
-        <v>98083</v>
+        <v>100379</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2991,21 +2991,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696777</v>
+        <v>696874</v>
       </c>
       <c r="R22" t="n">
-        <v>6660623</v>
+        <v>6660583</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3090,10 +3090,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121354210</v>
+        <v>121354241</v>
       </c>
       <c r="B23" t="n">
-        <v>98083</v>
+        <v>100288</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3106,21 +3106,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696874</v>
+        <v>696825</v>
       </c>
       <c r="R23" t="n">
-        <v>6660666</v>
+        <v>6660796</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3169,12 +3169,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3205,10 +3205,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121354154</v>
+        <v>121354251</v>
       </c>
       <c r="B24" t="n">
-        <v>100371</v>
+        <v>90157</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3221,21 +3221,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>4191</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum michelianum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Berk. &amp; Broome</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3254,10 +3254,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696874</v>
+        <v>696840</v>
       </c>
       <c r="R24" t="n">
-        <v>6660583</v>
+        <v>6660674</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3284,12 +3284,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3323,7 +3323,7 @@
         <v>121354202</v>
       </c>
       <c r="B25" t="n">
-        <v>100280</v>
+        <v>100288</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3435,10 +3435,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121354258</v>
+        <v>121354210</v>
       </c>
       <c r="B26" t="n">
-        <v>103619</v>
+        <v>98091</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3451,21 +3451,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222412</v>
+        <v>219798</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696953</v>
+        <v>696874</v>
       </c>
       <c r="R26" t="n">
-        <v>6660737</v>
+        <v>6660666</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3514,12 +3514,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3550,10 +3550,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121354251</v>
+        <v>121354141</v>
       </c>
       <c r="B27" t="n">
-        <v>90150</v>
+        <v>101282</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3566,21 +3566,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4191</v>
+        <v>221235</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Geastrum michelianum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Berk. &amp; Broome</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696840</v>
+        <v>696745</v>
       </c>
       <c r="R27" t="n">
-        <v>6660674</v>
+        <v>6660466</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3629,12 +3629,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3665,10 +3665,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121354226</v>
+        <v>121354249</v>
       </c>
       <c r="B28" t="n">
-        <v>98083</v>
+        <v>100288</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3681,21 +3681,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696779</v>
+        <v>696815</v>
       </c>
       <c r="R28" t="n">
-        <v>6660917</v>
+        <v>6660731</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3780,10 +3780,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121354234</v>
+        <v>121354158</v>
       </c>
       <c r="B29" t="n">
-        <v>100280</v>
+        <v>98091</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3796,21 +3796,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696786</v>
+        <v>696777</v>
       </c>
       <c r="R29" t="n">
-        <v>6660804</v>
+        <v>6660623</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3859,12 +3859,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3895,10 +3895,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121354245</v>
+        <v>121354239</v>
       </c>
       <c r="B30" t="n">
-        <v>100280</v>
+        <v>100288</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3944,10 +3944,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696963</v>
+        <v>696830</v>
       </c>
       <c r="R30" t="n">
-        <v>6660755</v>
+        <v>6660785</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4010,10 +4010,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121354199</v>
+        <v>121354218</v>
       </c>
       <c r="B31" t="n">
-        <v>100280</v>
+        <v>100288</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>696837</v>
+        <v>696810</v>
       </c>
       <c r="R31" t="n">
-        <v>6660782</v>
+        <v>6660842</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4089,12 +4089,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4125,10 +4125,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121354141</v>
+        <v>121354254</v>
       </c>
       <c r="B32" t="n">
-        <v>101274</v>
+        <v>100288</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4141,21 +4141,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696745</v>
+        <v>696815</v>
       </c>
       <c r="R32" t="n">
-        <v>6660466</v>
+        <v>6660713</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4204,12 +4204,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4240,10 +4240,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121354228</v>
+        <v>121354234</v>
       </c>
       <c r="B33" t="n">
-        <v>91653</v>
+        <v>100288</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4256,21 +4256,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4292,7 +4292,7 @@
         <v>696786</v>
       </c>
       <c r="R33" t="n">
-        <v>6660910</v>
+        <v>6660804</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4355,10 +4355,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121354148</v>
+        <v>121354156</v>
       </c>
       <c r="B34" t="n">
-        <v>101274</v>
+        <v>100379</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4371,21 +4371,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4404,10 +4404,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696853</v>
+        <v>696718</v>
       </c>
       <c r="R34" t="n">
-        <v>6660481</v>
+        <v>6660612</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4470,10 +4470,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121354237</v>
+        <v>121354143</v>
       </c>
       <c r="B35" t="n">
-        <v>100280</v>
+        <v>100379</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4486,21 +4486,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4519,10 +4519,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696816</v>
+        <v>696882</v>
       </c>
       <c r="R35" t="n">
-        <v>6660789</v>
+        <v>6660480</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4549,12 +4549,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 48490-2022 artfynd.xlsx
+++ b/artfynd/A 48490-2022 artfynd.xlsx
@@ -1940,10 +1940,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121354216</v>
+        <v>121354265</v>
       </c>
       <c r="B13" t="n">
-        <v>91661</v>
+        <v>100288</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696818</v>
+        <v>696849</v>
       </c>
       <c r="R13" t="n">
-        <v>6660846</v>
+        <v>6660766</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2055,10 +2055,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121354245</v>
+        <v>121354216</v>
       </c>
       <c r="B14" t="n">
-        <v>100288</v>
+        <v>91661</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,21 +2071,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696963</v>
+        <v>696818</v>
       </c>
       <c r="R14" t="n">
-        <v>6660755</v>
+        <v>6660846</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2170,7 +2170,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121354267</v>
+        <v>121354245</v>
       </c>
       <c r="B15" t="n">
         <v>100288</v>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696878</v>
+        <v>696963</v>
       </c>
       <c r="R15" t="n">
-        <v>6660770</v>
+        <v>6660755</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2285,7 +2285,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121354208</v>
+        <v>121354267</v>
       </c>
       <c r="B16" t="n">
         <v>100288</v>
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696843</v>
+        <v>696878</v>
       </c>
       <c r="R16" t="n">
-        <v>6660799</v>
+        <v>6660770</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2400,7 +2400,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121354265</v>
+        <v>121354208</v>
       </c>
       <c r="B17" t="n">
         <v>100288</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696849</v>
+        <v>696843</v>
       </c>
       <c r="R17" t="n">
-        <v>6660766</v>
+        <v>6660799</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2479,12 +2479,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 48490-2022 artfynd.xlsx
+++ b/artfynd/A 48490-2022 artfynd.xlsx
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121354226</v>
+        <v>121354152</v>
       </c>
       <c r="B7" t="n">
-        <v>98091</v>
+        <v>91661</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696779</v>
+        <v>696860</v>
       </c>
       <c r="R7" t="n">
-        <v>6660917</v>
+        <v>6660584</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121354258</v>
+        <v>121354226</v>
       </c>
       <c r="B8" t="n">
-        <v>103627</v>
+        <v>98091</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222412</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696953</v>
+        <v>696779</v>
       </c>
       <c r="R8" t="n">
-        <v>6660737</v>
+        <v>6660917</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121354152</v>
+        <v>121354247</v>
       </c>
       <c r="B9" t="n">
-        <v>91661</v>
+        <v>100288</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,21 +1496,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696860</v>
+        <v>696845</v>
       </c>
       <c r="R9" t="n">
-        <v>6660584</v>
+        <v>6660742</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121354247</v>
+        <v>121354258</v>
       </c>
       <c r="B10" t="n">
-        <v>100288</v>
+        <v>103627</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,16 +1611,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696845</v>
+        <v>696953</v>
       </c>
       <c r="R10" t="n">
-        <v>6660742</v>
+        <v>6660737</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121354265</v>
+        <v>121354216</v>
       </c>
       <c r="B13" t="n">
-        <v>100288</v>
+        <v>91661</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696849</v>
+        <v>696818</v>
       </c>
       <c r="R13" t="n">
-        <v>6660766</v>
+        <v>6660846</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2055,10 +2055,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121354216</v>
+        <v>121354245</v>
       </c>
       <c r="B14" t="n">
-        <v>91661</v>
+        <v>100288</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,21 +2071,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696818</v>
+        <v>696963</v>
       </c>
       <c r="R14" t="n">
-        <v>6660846</v>
+        <v>6660755</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2170,7 +2170,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121354245</v>
+        <v>121354267</v>
       </c>
       <c r="B15" t="n">
         <v>100288</v>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696963</v>
+        <v>696878</v>
       </c>
       <c r="R15" t="n">
-        <v>6660755</v>
+        <v>6660770</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2285,7 +2285,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121354267</v>
+        <v>121354208</v>
       </c>
       <c r="B16" t="n">
         <v>100288</v>
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696878</v>
+        <v>696843</v>
       </c>
       <c r="R16" t="n">
-        <v>6660770</v>
+        <v>6660799</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2400,7 +2400,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121354208</v>
+        <v>121354265</v>
       </c>
       <c r="B17" t="n">
         <v>100288</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696843</v>
+        <v>696849</v>
       </c>
       <c r="R17" t="n">
-        <v>6660799</v>
+        <v>6660766</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2479,12 +2479,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 48490-2022 artfynd.xlsx
+++ b/artfynd/A 48490-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121354234</v>
+        <v>121354167</v>
       </c>
       <c r="B2" t="n">
-        <v>100288</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +710,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>696786</v>
+        <v>696670</v>
       </c>
       <c r="R2" t="n">
-        <v>6660804</v>
+        <v>6660582</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,15 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121354228</v>
+        <v>121354251</v>
       </c>
       <c r="B3" t="n">
-        <v>91661</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91329</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,21 +796,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>4191</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Geastrum michelianum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Berk. &amp; Broome</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>696786</v>
+        <v>696840</v>
       </c>
       <c r="R3" t="n">
-        <v>6660910</v>
+        <v>6660674</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,15 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121354239</v>
+        <v>121354152</v>
       </c>
       <c r="B4" t="n">
-        <v>100288</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -921,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -945,7 +930,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>696830</v>
+        <v>696860</v>
       </c>
       <c r="R4" t="n">
-        <v>6660785</v>
+        <v>6660584</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,12 +969,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,15 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121354254</v>
+        <v>121354216</v>
       </c>
       <c r="B5" t="n">
-        <v>100288</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1060,7 +1040,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1069,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696815</v>
+        <v>696818</v>
       </c>
       <c r="R5" t="n">
-        <v>6660713</v>
+        <v>6660846</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,15 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121354208</v>
+        <v>121354228</v>
       </c>
       <c r="B6" t="n">
-        <v>100288</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,21 +1126,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1175,7 +1150,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1184,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696843</v>
+        <v>696786</v>
       </c>
       <c r="R6" t="n">
-        <v>6660799</v>
+        <v>6660910</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,12 +1189,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,15 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121354245</v>
+        <v>121354158</v>
       </c>
       <c r="B7" t="n">
-        <v>100288</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,21 +1236,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1299,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696963</v>
+        <v>696777</v>
       </c>
       <c r="R7" t="n">
-        <v>6660755</v>
+        <v>6660623</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,12 +1299,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,15 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121354223</v>
+        <v>121354189</v>
       </c>
       <c r="B8" t="n">
-        <v>100288</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,21 +1346,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1414,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696708</v>
+        <v>696492</v>
       </c>
       <c r="R8" t="n">
-        <v>6660830</v>
+        <v>6660752</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,12 +1409,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,15 +1445,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121354247</v>
+        <v>121354204</v>
       </c>
       <c r="B9" t="n">
-        <v>100288</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1496,21 +1456,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222771</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1529,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696845</v>
+        <v>696959</v>
       </c>
       <c r="R9" t="n">
-        <v>6660742</v>
+        <v>6660847</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,12 +1519,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,15 +1555,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121354204</v>
+        <v>121354206</v>
       </c>
       <c r="B10" t="n">
-        <v>98091</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1644,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696959</v>
+        <v>696910</v>
       </c>
       <c r="R10" t="n">
-        <v>6660847</v>
+        <v>6660863</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,15 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121354152</v>
+        <v>121354210</v>
       </c>
       <c r="B11" t="n">
-        <v>91661</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1726,21 +1676,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1750,7 +1700,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1759,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>696860</v>
+        <v>696874</v>
       </c>
       <c r="R11" t="n">
-        <v>6660584</v>
+        <v>6660666</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,15 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121354216</v>
+        <v>121354226</v>
       </c>
       <c r="B12" t="n">
-        <v>91661</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,21 +1786,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4769</v>
+        <v>219798</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1865,7 +1810,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1874,10 +1819,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696818</v>
+        <v>696779</v>
       </c>
       <c r="R12" t="n">
-        <v>6660846</v>
+        <v>6660917</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,15 +1885,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121354226</v>
+        <v>121354230</v>
       </c>
       <c r="B13" t="n">
-        <v>98091</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1989,10 +1929,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696779</v>
+        <v>696816</v>
       </c>
       <c r="R13" t="n">
-        <v>6660917</v>
+        <v>6660877</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2055,37 +1995,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121354265</v>
+        <v>121354141</v>
       </c>
       <c r="B14" t="n">
-        <v>100288</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2104,10 +2039,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696849</v>
+        <v>696745</v>
       </c>
       <c r="R14" t="n">
-        <v>6660766</v>
+        <v>6660466</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2134,12 +2069,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,37 +2105,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121354256</v>
+        <v>121354148</v>
       </c>
       <c r="B15" t="n">
-        <v>100288</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2219,10 +2149,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696843</v>
+        <v>696853</v>
       </c>
       <c r="R15" t="n">
-        <v>6660663</v>
+        <v>6660481</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2249,12 +2179,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,37 +2215,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121354258</v>
+        <v>121354180</v>
       </c>
       <c r="B16" t="n">
-        <v>103627</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2334,10 +2259,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696953</v>
+        <v>696555</v>
       </c>
       <c r="R16" t="n">
-        <v>6660737</v>
+        <v>6660719</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2364,12 +2289,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2400,15 +2325,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121354165</v>
+        <v>121354258</v>
       </c>
       <c r="B17" t="n">
-        <v>100379</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2416,21 +2336,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2449,10 +2369,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696683</v>
+        <v>696953</v>
       </c>
       <c r="R17" t="n">
-        <v>6660536</v>
+        <v>6660737</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2479,12 +2399,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2515,15 +2435,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121354154</v>
+        <v>121354143</v>
       </c>
       <c r="B18" t="n">
-        <v>100379</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2564,10 +2479,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696874</v>
+        <v>696882</v>
       </c>
       <c r="R18" t="n">
-        <v>6660583</v>
+        <v>6660480</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2630,15 +2545,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121354202</v>
+        <v>121354154</v>
       </c>
       <c r="B19" t="n">
-        <v>100288</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2646,21 +2556,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2679,10 +2589,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696939</v>
+        <v>696874</v>
       </c>
       <c r="R19" t="n">
-        <v>6660882</v>
+        <v>6660583</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2745,15 +2655,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121354158</v>
+        <v>121354156</v>
       </c>
       <c r="B20" t="n">
-        <v>98091</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,21 +2666,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2794,10 +2699,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696777</v>
+        <v>696718</v>
       </c>
       <c r="R20" t="n">
-        <v>6660623</v>
+        <v>6660612</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2860,15 +2765,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121354249</v>
+        <v>121354165</v>
       </c>
       <c r="B21" t="n">
-        <v>100288</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2876,21 +2776,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2909,10 +2809,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696815</v>
+        <v>696683</v>
       </c>
       <c r="R21" t="n">
-        <v>6660731</v>
+        <v>6660536</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2939,12 +2839,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2975,15 +2875,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121354267</v>
+        <v>121354169</v>
       </c>
       <c r="B22" t="n">
-        <v>100288</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2991,21 +2886,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3024,10 +2919,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696878</v>
+        <v>696652</v>
       </c>
       <c r="R22" t="n">
-        <v>6660770</v>
+        <v>6660592</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3054,12 +2949,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3090,15 +2985,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121354213</v>
+        <v>121354175</v>
       </c>
       <c r="B23" t="n">
-        <v>100288</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3106,21 +2996,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3139,10 +3029,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696829</v>
+        <v>696541</v>
       </c>
       <c r="R23" t="n">
-        <v>6660866</v>
+        <v>6660698</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3169,12 +3059,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3205,15 +3095,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121354241</v>
+        <v>121354194</v>
       </c>
       <c r="B24" t="n">
-        <v>100288</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3221,21 +3106,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3254,10 +3139,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696825</v>
+        <v>696604</v>
       </c>
       <c r="R24" t="n">
-        <v>6660796</v>
+        <v>6660692</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3284,12 +3169,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3320,15 +3205,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121354206</v>
+        <v>121354186</v>
       </c>
       <c r="B25" t="n">
-        <v>98091</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3336,21 +3216,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3369,10 +3249,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696910</v>
+        <v>696498</v>
       </c>
       <c r="R25" t="n">
-        <v>6660863</v>
+        <v>6660749</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3435,15 +3315,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121354237</v>
+        <v>121354192</v>
       </c>
       <c r="B26" t="n">
-        <v>100288</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3484,10 +3359,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696816</v>
+        <v>696569</v>
       </c>
       <c r="R26" t="n">
-        <v>6660789</v>
+        <v>6660718</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3514,12 +3389,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3550,15 +3425,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121354230</v>
+        <v>121354199</v>
       </c>
       <c r="B27" t="n">
-        <v>98091</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3566,21 +3436,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3599,10 +3469,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696816</v>
+        <v>696837</v>
       </c>
       <c r="R27" t="n">
-        <v>6660877</v>
+        <v>6660782</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3629,12 +3499,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2022-09-15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3665,15 +3535,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121354210</v>
+        <v>121354202</v>
       </c>
       <c r="B28" t="n">
-        <v>98091</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3681,21 +3546,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219798</v>
+        <v>222771</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3714,10 +3579,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696874</v>
+        <v>696939</v>
       </c>
       <c r="R28" t="n">
-        <v>6660666</v>
+        <v>6660882</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3780,15 +3645,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121354143</v>
+        <v>121354208</v>
       </c>
       <c r="B29" t="n">
-        <v>100379</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3796,21 +3656,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3829,10 +3689,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696882</v>
+        <v>696843</v>
       </c>
       <c r="R29" t="n">
-        <v>6660480</v>
+        <v>6660799</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3895,15 +3755,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121354199</v>
+        <v>121354213</v>
       </c>
       <c r="B30" t="n">
-        <v>100288</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3944,10 +3799,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696837</v>
+        <v>696829</v>
       </c>
       <c r="R30" t="n">
-        <v>6660782</v>
+        <v>6660866</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3974,12 +3829,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4013,12 +3868,7 @@
         <v>121354218</v>
       </c>
       <c r="B31" t="n">
-        <v>100288</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4125,15 +3975,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121354148</v>
+        <v>121354223</v>
       </c>
       <c r="B32" t="n">
-        <v>101282</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4141,21 +3986,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4174,10 +4019,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696853</v>
+        <v>696708</v>
       </c>
       <c r="R32" t="n">
-        <v>6660481</v>
+        <v>6660830</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4204,12 +4049,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4240,15 +4085,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121354251</v>
+        <v>121354234</v>
       </c>
       <c r="B33" t="n">
-        <v>90157</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4256,21 +4096,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4191</v>
+        <v>222771</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Geastrum michelianum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Berk. &amp; Broome</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4280,7 +4120,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4289,10 +4129,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696840</v>
+        <v>696786</v>
       </c>
       <c r="R33" t="n">
-        <v>6660674</v>
+        <v>6660804</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4355,15 +4195,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121354156</v>
+        <v>121354237</v>
       </c>
       <c r="B34" t="n">
-        <v>100379</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4371,21 +4206,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4404,10 +4239,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696718</v>
+        <v>696816</v>
       </c>
       <c r="R34" t="n">
-        <v>6660612</v>
+        <v>6660789</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4434,12 +4269,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4470,15 +4305,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121354141</v>
+        <v>121354239</v>
       </c>
       <c r="B35" t="n">
-        <v>101282</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4486,21 +4316,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4519,10 +4349,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696745</v>
+        <v>696830</v>
       </c>
       <c r="R35" t="n">
-        <v>6660466</v>
+        <v>6660785</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4549,12 +4379,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4578,6 +4408,886 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr">
+        <is>
+          <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>121354241</v>
+      </c>
+      <c r="B36" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Sälgmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>696825</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6660796</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jake Bull</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>121354245</v>
+      </c>
+      <c r="B37" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Sälgmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>696963</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6660755</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jake Bull</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>121354247</v>
+      </c>
+      <c r="B38" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Sälgmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>696845</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6660742</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jake Bull</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>121354249</v>
+      </c>
+      <c r="B39" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Sälgmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>696815</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6660731</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jake Bull</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>121354254</v>
+      </c>
+      <c r="B40" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Sälgmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>696815</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6660713</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jake Bull</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>121354256</v>
+      </c>
+      <c r="B41" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Sälgmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>696843</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6660663</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jake Bull</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>121354265</v>
+      </c>
+      <c r="B42" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Sälgmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>696849</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6660766</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jake Bull</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>121354267</v>
+      </c>
+      <c r="B43" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Sälgmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>696878</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6660770</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Jake Bull</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
         <is>
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>

--- a/artfynd/A 48490-2022 artfynd.xlsx
+++ b/artfynd/A 48490-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354167</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354251</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354152</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354216</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354228</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,6 +1362,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354158</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1442,6 +1477,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354189</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1552,6 +1592,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354204</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1662,6 +1707,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354206</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1772,6 +1822,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354210</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1882,6 +1937,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354226</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1992,6 +2052,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354230</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2102,6 +2167,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354141</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2212,6 +2282,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354148</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2322,6 +2397,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354180</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2432,6 +2512,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354258</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2542,6 +2627,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354143</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2652,6 +2742,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354154</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2762,6 +2857,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354156</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2872,6 +2972,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354165</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2982,6 +3087,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354169</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3092,6 +3202,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354175</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3202,6 +3317,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354194</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3312,6 +3432,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354186</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3422,6 +3547,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354192</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3532,6 +3662,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354199</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3642,6 +3777,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354202</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3752,6 +3892,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354208</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3862,6 +4007,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354213</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3972,6 +4122,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354218</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4082,6 +4237,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354223</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4192,6 +4352,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354234</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4302,6 +4467,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354237</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4412,6 +4582,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354239</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4522,6 +4697,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354241</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4632,6 +4812,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354245</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4742,6 +4927,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354247</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4852,6 +5042,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354249</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4962,6 +5157,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354254</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5072,6 +5272,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354256</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5182,6 +5387,11 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354265</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5292,8 +5502,57 @@
           <t>Alight AB - NVI och skötselplan Berga solcellspark</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121354267</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>